--- a/fsae_A_2025_track_xy.xlsx
+++ b/fsae_A_2025_track_xy.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C399"/>
+  <dimension ref="A1:C389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,10 +438,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>105.3211487141915</v>
+        <v>105.3216911527175</v>
       </c>
     </row>
     <row r="3">
@@ -449,10 +449,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.2380915043490268</v>
+        <v>-0.4725621883273945</v>
       </c>
       <c r="C3" t="n">
-        <v>106.510811091926</v>
+        <v>108.0631512569737</v>
       </c>
     </row>
     <row r="4">
@@ -460,10 +460,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.09766467994392869</v>
+        <v>0.5097087179979294</v>
       </c>
       <c r="C4" t="n">
-        <v>107.6766806910447</v>
+        <v>110.6658541581231</v>
       </c>
     </row>
     <row r="5">
@@ -471,10 +471,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.9320265908474246</v>
+        <v>2.675724812362666</v>
       </c>
       <c r="C5" t="n">
-        <v>108.5574896028262</v>
+        <v>112.4115038377604</v>
       </c>
     </row>
     <row r="6">
@@ -482,10 +482,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.078016206339659</v>
+        <v>5.427707248899626</v>
       </c>
       <c r="C6" t="n">
-        <v>108.9558511705308</v>
+        <v>112.8183345077656</v>
       </c>
     </row>
     <row r="7">
@@ -493,10 +493,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>2.078016206339662</v>
+        <v>5.427707248899576</v>
       </c>
       <c r="C7" t="n">
-        <v>108.9558511705307</v>
+        <v>112.8183345077655</v>
       </c>
     </row>
     <row r="8">
@@ -504,10 +504,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>9.85676569488716</v>
+        <v>12.17982106034236</v>
       </c>
       <c r="C8" t="n">
-        <v>110.5161484160904</v>
+        <v>112.939781832273</v>
       </c>
     </row>
     <row r="9">
@@ -515,10 +515,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>17.15580348430143</v>
+        <v>18.64718057958457</v>
       </c>
       <c r="C9" t="n">
-        <v>113.625411745045</v>
+        <v>114.8837600276687</v>
       </c>
     </row>
     <row r="10">
@@ -526,10 +526,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>23.67021740379447</v>
+        <v>24.3472482052315</v>
       </c>
       <c r="C10" t="n">
-        <v>118.1537538683386</v>
+        <v>118.5052265038851</v>
       </c>
     </row>
     <row r="11">
@@ -537,10 +537,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>29.12787239297709</v>
+        <v>28.85473492224019</v>
       </c>
       <c r="C11" t="n">
-        <v>123.9120064782134</v>
+        <v>123.5339792191512</v>
       </c>
     </row>
     <row r="12">
@@ -548,10 +548,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>29.12787239297734</v>
+        <v>28.85473492223992</v>
       </c>
       <c r="C12" t="n">
-        <v>123.9120064782132</v>
+        <v>123.5339792191513</v>
       </c>
     </row>
     <row r="13">
@@ -559,10 +559,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>31.52560099717608</v>
+        <v>31.22079916885096</v>
       </c>
       <c r="C13" t="n">
-        <v>125.9432770552858</v>
+        <v>125.7715036107082</v>
       </c>
     </row>
     <row r="14">
@@ -570,10 +570,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>34.54621083834996</v>
+        <v>34.31358275002227</v>
       </c>
       <c r="C14" t="n">
-        <v>126.8099250830787</v>
+        <v>126.7910452439631</v>
       </c>
     </row>
     <row r="15">
@@ -581,10 +581,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>37.65614812562676</v>
+        <v>37.54642046502172</v>
       </c>
       <c r="C15" t="n">
-        <v>126.3588677853002</v>
+        <v>126.3992088873293</v>
       </c>
     </row>
     <row r="16">
@@ -592,10 +592,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>40.30608046712213</v>
+        <v>40.30608046712361</v>
       </c>
       <c r="C16" t="n">
-        <v>124.6697789178421</v>
+        <v>124.6703213563713</v>
       </c>
     </row>
     <row r="17">
@@ -603,10 +603,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>40.30608046712209</v>
+        <v>40.30608046712154</v>
       </c>
       <c r="C17" t="n">
-        <v>124.6697789178423</v>
+        <v>124.6703213563693</v>
       </c>
     </row>
     <row r="18">
@@ -614,10 +614,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>44.10546744953939</v>
+        <v>44.10546744953864</v>
       </c>
       <c r="C18" t="n">
-        <v>122.6554006519865</v>
+        <v>122.655943090513</v>
       </c>
     </row>
     <row r="19">
@@ -625,10 +625,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>48.38607405118213</v>
+        <v>48.38607405118145</v>
       </c>
       <c r="C19" t="n">
-        <v>123.0670660040468</v>
+        <v>123.0676084425728</v>
       </c>
     </row>
     <row r="20">
@@ -636,10 +636,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>51.731932249233</v>
+        <v>51.73193224923262</v>
       </c>
       <c r="C20" t="n">
-        <v>125.7686015227195</v>
+        <v>125.7691439612452</v>
       </c>
     </row>
     <row r="21">
@@ -650,7 +650,7 @@
         <v>53.03627642418778</v>
       </c>
       <c r="C21" t="n">
-        <v>129.8663750051579</v>
+        <v>129.8669174436836</v>
       </c>
     </row>
     <row r="22">
@@ -658,10 +658,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>53.03627642418776</v>
+        <v>53.03627642418791</v>
       </c>
       <c r="C22" t="n">
-        <v>129.8663750051552</v>
+        <v>129.8669174436836</v>
       </c>
     </row>
     <row r="23">
@@ -669,10 +669,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>54.3406205991422</v>
+        <v>54.34062059914306</v>
       </c>
       <c r="C23" t="n">
-        <v>133.964148487595</v>
+        <v>133.964690926122</v>
       </c>
     </row>
     <row r="24">
@@ -680,10 +680,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>57.68647879719402</v>
+        <v>57.68647879719427</v>
       </c>
       <c r="C24" t="n">
-        <v>136.6656840062684</v>
+        <v>136.6662264447944</v>
       </c>
     </row>
     <row r="25">
@@ -691,10 +691,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>61.96708539883801</v>
+        <v>61.96708539883713</v>
       </c>
       <c r="C25" t="n">
-        <v>137.077349358328</v>
+        <v>137.0778917968543</v>
       </c>
     </row>
     <row r="26">
@@ -702,10 +702,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>65.7664723812556</v>
+        <v>65.76647238125429</v>
       </c>
       <c r="C26" t="n">
-        <v>135.0629710924702</v>
+        <v>135.063513530998</v>
       </c>
     </row>
     <row r="27">
@@ -713,10 +713,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>65.76647238125496</v>
+        <v>65.76647238125433</v>
       </c>
       <c r="C27" t="n">
-        <v>135.0629710924708</v>
+        <v>135.0635135309981</v>
       </c>
     </row>
     <row r="28">
@@ -724,10 +724,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>69.56585936367205</v>
+        <v>69.56585936367142</v>
       </c>
       <c r="C28" t="n">
-        <v>133.0485928266153</v>
+        <v>133.0491352651418</v>
       </c>
     </row>
     <row r="29">
@@ -735,10 +735,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>73.84646596531442</v>
+        <v>73.84646596531422</v>
       </c>
       <c r="C29" t="n">
-        <v>133.4602581786757</v>
+        <v>133.4608006172017</v>
       </c>
     </row>
     <row r="30">
@@ -746,10 +746,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>77.19232416336503</v>
+        <v>77.19232416336538</v>
       </c>
       <c r="C30" t="n">
-        <v>136.1617936973481</v>
+        <v>136.1623361358741</v>
       </c>
     </row>
     <row r="31">
@@ -757,10 +757,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>78.49666833831975</v>
+        <v>78.4966683383205</v>
       </c>
       <c r="C31" t="n">
-        <v>140.2595671797863</v>
+        <v>140.2601096183124</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>78.49666833831975</v>
+        <v>78.4966683383205</v>
       </c>
       <c r="C32" t="n">
-        <v>140.2595671797863</v>
+        <v>140.2601096183124</v>
       </c>
     </row>
     <row r="33">
@@ -779,10 +779,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>78.44005008418742</v>
+        <v>78.44005008418823</v>
       </c>
       <c r="C33" t="n">
-        <v>141.3093232227822</v>
+        <v>141.3098656613085</v>
       </c>
     </row>
     <row r="34">
@@ -790,10 +790,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>78.23675975900298</v>
+        <v>78.23675975900377</v>
       </c>
       <c r="C34" t="n">
-        <v>142.3407622273742</v>
+        <v>142.3413046659007</v>
       </c>
     </row>
     <row r="35">
@@ -801,10 +801,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>77.89081614343917</v>
+        <v>77.89081614343991</v>
       </c>
       <c r="C35" t="n">
-        <v>143.3334940095581</v>
+        <v>143.3340364480848</v>
       </c>
     </row>
     <row r="36">
@@ -812,10 +812,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>77.40905808491696</v>
+        <v>77.40905808491762</v>
       </c>
       <c r="C36" t="n">
-        <v>144.2678935758874</v>
+        <v>144.2684360144143</v>
       </c>
     </row>
     <row r="37">
@@ -823,10 +823,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>77.40905808491704</v>
+        <v>77.40905808491743</v>
       </c>
       <c r="C37" t="n">
-        <v>144.2678935758874</v>
+        <v>144.2684360144141</v>
       </c>
     </row>
     <row r="38">
@@ -834,10 +834,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>76.78071117920825</v>
+        <v>76.79862628102902</v>
       </c>
       <c r="C38" t="n">
-        <v>147.3959017559185</v>
+        <v>147.506196203525</v>
       </c>
     </row>
     <row r="39">
@@ -845,10 +845,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>78.30490174771805</v>
+        <v>78.47488399209323</v>
       </c>
       <c r="C39" t="n">
-        <v>150.1987749459007</v>
+        <v>150.3427219156397</v>
       </c>
     </row>
     <row r="40">
@@ -856,10 +856,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>81.27201619290864</v>
+        <v>81.60555783160343</v>
       </c>
       <c r="C40" t="n">
-        <v>151.3715864727015</v>
+        <v>151.3696587880892</v>
       </c>
     </row>
     <row r="41">
@@ -867,10 +867,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>84.30066245052087</v>
+        <v>84.63624688539312</v>
       </c>
       <c r="C41" t="n">
-        <v>150.3683134019442</v>
+        <v>150.0771256594502</v>
       </c>
     </row>
     <row r="42">
@@ -878,10 +878,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>84.30066245052114</v>
+        <v>84.63624688539304</v>
       </c>
       <c r="C42" t="n">
-        <v>150.3683134019445</v>
+        <v>150.0771256594501</v>
       </c>
     </row>
     <row r="43">
@@ -889,10 +889,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>88.84960681986115</v>
+        <v>87.90411928664258</v>
       </c>
       <c r="C43" t="n">
-        <v>147.6656769541132</v>
+        <v>147.7474756441659</v>
       </c>
     </row>
     <row r="44">
@@ -900,10 +900,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>93.94604347465149</v>
+        <v>91.69868973086328</v>
       </c>
       <c r="C44" t="n">
-        <v>146.2431889688543</v>
+        <v>146.4407643644988</v>
       </c>
     </row>
     <row r="45">
@@ -911,10 +911,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>99.23709404705109</v>
+        <v>95.7080728044717</v>
       </c>
       <c r="C45" t="n">
-        <v>146.19934281958</v>
+        <v>146.2643937500964</v>
       </c>
     </row>
     <row r="46">
@@ -922,10 +922,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>104.3564050597931</v>
+        <v>99.60272709652075</v>
       </c>
       <c r="C46" t="n">
-        <v>147.5371744230769</v>
+        <v>147.2328601511585</v>
       </c>
     </row>
     <row r="47">
@@ -933,10 +933,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>104.3564050597932</v>
+        <v>99.60272709652071</v>
       </c>
       <c r="C47" t="n">
-        <v>147.5371744230769</v>
+        <v>147.2328601511585</v>
       </c>
     </row>
     <row r="48">
@@ -944,10 +944,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>146.7698366528759</v>
+        <v>150.3995999561568</v>
       </c>
       <c r="C48" t="n">
-        <v>164.8507706481096</v>
+        <v>167.9686627766998</v>
       </c>
     </row>
     <row r="49">
@@ -955,10 +955,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>146.7698366528758</v>
+        <v>150.3995999561568</v>
       </c>
       <c r="C49" t="n">
-        <v>164.8507706481097</v>
+        <v>167.9686627766999</v>
       </c>
     </row>
     <row r="50">
@@ -966,10 +966,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>151.4018148824133</v>
+        <v>153.8954358404129</v>
       </c>
       <c r="C50" t="n">
-        <v>167.4981953392061</v>
+        <v>170.0225331239814</v>
       </c>
     </row>
     <row r="51">
@@ -977,10 +977,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>155.1849187168789</v>
+        <v>156.6661248707191</v>
       </c>
       <c r="C51" t="n">
-        <v>171.2601370175937</v>
+        <v>172.9826909289701</v>
       </c>
     </row>
     <row r="52">
@@ -988,10 +988,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>157.858284865338</v>
+        <v>158.4846093810662</v>
       </c>
       <c r="C52" t="n">
-        <v>175.8771916252641</v>
+        <v>176.6065515800882</v>
       </c>
     </row>
     <row r="53">
@@ -999,10 +999,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>159.2375718130256</v>
+        <v>159.2018647627461</v>
       </c>
       <c r="C53" t="n">
-        <v>181.0309909354698</v>
+        <v>180.5971400893868</v>
       </c>
     </row>
     <row r="54">
@@ -1010,10 +1010,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>159.2375718130257</v>
+        <v>159.2018647627461</v>
       </c>
       <c r="C54" t="n">
-        <v>181.0309909354697</v>
+        <v>180.5971400893867</v>
       </c>
     </row>
     <row r="55">
@@ -1021,10 +1021,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>160.3323187084424</v>
+        <v>160.1255782523695</v>
       </c>
       <c r="C55" t="n">
-        <v>183.4491144489841</v>
+        <v>183.1963713765003</v>
       </c>
     </row>
     <row r="56">
@@ -1032,10 +1032,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>162.5881713920604</v>
+        <v>162.3788930884603</v>
       </c>
       <c r="C56" t="n">
-        <v>184.8480142886615</v>
+        <v>184.7875414316094</v>
       </c>
     </row>
     <row r="57">
@@ -1043,10 +1043,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>165.2408888567559</v>
+        <v>165.1373798129893</v>
       </c>
       <c r="C57" t="n">
-        <v>184.7537691607473</v>
+        <v>184.7884823990929</v>
       </c>
     </row>
     <row r="58">
@@ -1054,10 +1054,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>167.3917796757545</v>
+        <v>167.3917796757547</v>
       </c>
       <c r="C58" t="n">
-        <v>183.1983075648268</v>
+        <v>183.198850003353</v>
       </c>
     </row>
     <row r="59">
@@ -1065,10 +1065,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>167.3917796757542</v>
+        <v>167.3917796757543</v>
       </c>
       <c r="C59" t="n">
-        <v>183.1983075648266</v>
+        <v>183.1988500033526</v>
       </c>
     </row>
     <row r="60">
@@ -1076,10 +1076,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>170.2865540878347</v>
+        <v>170.2865540878348</v>
       </c>
       <c r="C60" t="n">
-        <v>180.7041251968863</v>
+        <v>180.7046676354123</v>
       </c>
     </row>
     <row r="61">
@@ -1087,10 +1087,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>173.9472233932257</v>
+        <v>173.9472233932258</v>
       </c>
       <c r="C61" t="n">
-        <v>179.6086048557019</v>
+        <v>179.6091472942279</v>
       </c>
     </row>
     <row r="62">
@@ -1101,7 +1101,7 @@
         <v>177.7362457493302</v>
       </c>
       <c r="C62" t="n">
-        <v>180.1025422670421</v>
+        <v>180.1030847055681</v>
       </c>
     </row>
     <row r="63">
@@ -1109,10 +1109,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>180.9937253575861</v>
+        <v>180.9937253575862</v>
       </c>
       <c r="C63" t="n">
-        <v>182.0999133350154</v>
+        <v>182.1004557735414</v>
       </c>
     </row>
     <row r="64">
@@ -1120,10 +1120,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>180.993725357586</v>
+        <v>180.9937253575862</v>
       </c>
       <c r="C64" t="n">
-        <v>182.0999133350153</v>
+        <v>182.1004557735414</v>
       </c>
     </row>
     <row r="65">
@@ -1131,10 +1131,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>182.3322189204874</v>
+        <v>182.3322189204876</v>
       </c>
       <c r="C65" t="n">
-        <v>183.1539905457631</v>
+        <v>183.1545329842892</v>
       </c>
     </row>
     <row r="66">
@@ -1142,10 +1142,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>183.842826094747</v>
+        <v>183.8428260947472</v>
       </c>
       <c r="C66" t="n">
-        <v>183.9418418954615</v>
+        <v>183.9423843339875</v>
       </c>
     </row>
     <row r="67">
@@ -1153,10 +1153,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>185.4732445720615</v>
+        <v>185.4732445720617</v>
       </c>
       <c r="C67" t="n">
-        <v>184.4361893167933</v>
+        <v>184.4367317553194</v>
       </c>
     </row>
     <row r="68">
@@ -1164,10 +1164,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>187.1670237732751</v>
+        <v>187.1670237732753</v>
       </c>
       <c r="C68" t="n">
-        <v>184.6199168370028</v>
+        <v>184.6204592755289</v>
       </c>
     </row>
     <row r="69">
@@ -1175,10 +1175,10 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>187.1670237732751</v>
+        <v>187.1670237732752</v>
       </c>
       <c r="C69" t="n">
-        <v>184.6199168370029</v>
+        <v>184.620459275529</v>
       </c>
     </row>
     <row r="70">
@@ -1186,10 +1186,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>189.4264939604836</v>
+        <v>189.4264939604837</v>
       </c>
       <c r="C70" t="n">
-        <v>184.8650059573473</v>
+        <v>184.8655483958734</v>
       </c>
     </row>
     <row r="71">
@@ -1197,10 +1197,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>191.6014421116514</v>
+        <v>191.6014421116515</v>
       </c>
       <c r="C71" t="n">
-        <v>185.524456291737</v>
+        <v>185.5249987302631</v>
       </c>
     </row>
     <row r="72">
@@ -1211,7 +1211,7 @@
         <v>193.6165641962639</v>
       </c>
       <c r="C72" t="n">
-        <v>186.5754354484772</v>
+        <v>186.5759778870032</v>
       </c>
     </row>
     <row r="73">
@@ -1219,10 +1219,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>195.4020899005464</v>
+        <v>195.4020899005465</v>
       </c>
       <c r="C73" t="n">
-        <v>187.9815549893205</v>
+        <v>187.9820974278466</v>
       </c>
     </row>
     <row r="74">
@@ -1233,7 +1233,7 @@
         <v>195.4020899005459</v>
       </c>
       <c r="C74" t="n">
-        <v>187.9815549893208</v>
+        <v>187.9820974278468</v>
       </c>
     </row>
     <row r="75">
@@ -1241,10 +1241,10 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>197.2389367506735</v>
+        <v>197.2389367506736</v>
       </c>
       <c r="C75" t="n">
-        <v>189.4280904512893</v>
+        <v>189.4286328898154</v>
       </c>
     </row>
     <row r="76">
@@ -1252,10 +1252,10 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>199.3119792416694</v>
+        <v>199.3119792416695</v>
       </c>
       <c r="C76" t="n">
-        <v>190.5092777727475</v>
+        <v>190.5098202112735</v>
       </c>
     </row>
     <row r="77">
@@ -1263,10 +1263,10 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>201.5494416602062</v>
+        <v>201.5494416602063</v>
       </c>
       <c r="C77" t="n">
-        <v>191.1876826070403</v>
+        <v>191.1882250455664</v>
       </c>
     </row>
     <row r="78">
@@ -1274,10 +1274,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>203.8738555212763</v>
+        <v>203.8738555212764</v>
       </c>
       <c r="C78" t="n">
-        <v>191.4398162938449</v>
+        <v>191.440358732371</v>
       </c>
     </row>
     <row r="79">
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>203.8738555212763</v>
+        <v>203.8738555212764</v>
       </c>
       <c r="C79" t="n">
-        <v>191.4398162938443</v>
+        <v>191.4403587323704</v>
       </c>
     </row>
     <row r="80">
@@ -1296,10 +1296,10 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>205.9880026489653</v>
+        <v>205.9880026489654</v>
       </c>
       <c r="C80" t="n">
-        <v>191.6506299116084</v>
+        <v>191.6511723501345</v>
       </c>
     </row>
     <row r="81">
@@ -1307,10 +1307,10 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>208.0365620002394</v>
+        <v>208.0365620002395</v>
       </c>
       <c r="C81" t="n">
-        <v>192.2140702751413</v>
+        <v>192.2146127136674</v>
       </c>
     </row>
     <row r="82">
@@ -1318,10 +1318,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>209.961151151531</v>
+        <v>209.9611511515311</v>
       </c>
       <c r="C82" t="n">
-        <v>193.1140797515811</v>
+        <v>193.1146221901072</v>
       </c>
     </row>
     <row r="83">
@@ -1329,10 +1329,10 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>211.7069207381124</v>
+        <v>211.7069207381125</v>
       </c>
       <c r="C83" t="n">
-        <v>194.3250087377392</v>
+        <v>194.3255511762653</v>
       </c>
     </row>
     <row r="84">
@@ -1340,10 +1340,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>211.7069207381123</v>
+        <v>211.7069207381126</v>
       </c>
       <c r="C84" t="n">
-        <v>194.3250087377392</v>
+        <v>194.3255511762653</v>
       </c>
     </row>
     <row r="85">
@@ -1351,10 +1351,10 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>214.0154152686653</v>
+        <v>214.0154152686606</v>
       </c>
       <c r="C85" t="n">
-        <v>195.9784630137505</v>
+        <v>195.979005452276</v>
       </c>
     </row>
     <row r="86">
@@ -1362,10 +1362,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>216.5304817001633</v>
+        <v>216.5304817001542</v>
       </c>
       <c r="C86" t="n">
-        <v>197.2966052236828</v>
+        <v>197.297147662207</v>
       </c>
     </row>
     <row r="87">
@@ -1373,10 +1373,10 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>219.2037386091128</v>
+        <v>219.2037386090999</v>
       </c>
       <c r="C87" t="n">
-        <v>198.2540787424845</v>
+        <v>198.2546211810067</v>
       </c>
     </row>
     <row r="88">
@@ -1384,10 +1384,10 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>221.9837615190075</v>
+        <v>221.9837615189908</v>
       </c>
       <c r="C88" t="n">
-        <v>198.8324649982975</v>
+        <v>198.8330074368166</v>
       </c>
     </row>
     <row r="89">
@@ -1395,10 +1395,10 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>221.9837615190076</v>
+        <v>221.9837615189908</v>
       </c>
       <c r="C89" t="n">
-        <v>198.8324649982976</v>
+        <v>198.8330074368167</v>
       </c>
     </row>
     <row r="90">
@@ -1406,10 +1406,10 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>223.5182647719534</v>
+        <v>223.5182647719416</v>
       </c>
       <c r="C90" t="n">
-        <v>199.1070679059435</v>
+        <v>199.1076103444624</v>
       </c>
     </row>
     <row r="91">
@@ -1417,10 +1417,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>225.0248341122709</v>
+        <v>225.0248341122639</v>
       </c>
       <c r="C91" t="n">
-        <v>199.5075124252017</v>
+        <v>199.5080548637218</v>
       </c>
     </row>
     <row r="92">
@@ -1428,10 +1428,10 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>226.4931680260697</v>
+        <v>226.4931680260671</v>
       </c>
       <c r="C92" t="n">
-        <v>200.0310604246983</v>
+        <v>200.031602863221</v>
       </c>
     </row>
     <row r="93">
@@ -1439,10 +1439,10 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>227.91322644297</v>
+        <v>227.913226442971</v>
       </c>
       <c r="C93" t="n">
-        <v>200.6741320247394</v>
+        <v>200.6746744632658</v>
       </c>
     </row>
     <row r="94">
@@ -1450,10 +1450,10 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>227.9132264429701</v>
+        <v>227.9132264429709</v>
       </c>
       <c r="C94" t="n">
-        <v>200.6741320247393</v>
+        <v>200.6746744632658</v>
       </c>
     </row>
     <row r="95">
@@ -1461,10 +1461,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>291.8543211674651</v>
+        <v>291.8543211670005</v>
       </c>
       <c r="C95" t="n">
-        <v>232.8791949221958</v>
+        <v>232.8797373606178</v>
       </c>
     </row>
     <row r="96">
@@ -1472,10 +1472,10 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>291.8543211674667</v>
+        <v>291.8543211670006</v>
       </c>
       <c r="C96" t="n">
-        <v>232.8791949221927</v>
+        <v>232.8797373606179</v>
       </c>
     </row>
     <row r="97">
@@ -1483,10 +1483,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>297.2164307326175</v>
+        <v>297.2164307322597</v>
       </c>
       <c r="C97" t="n">
-        <v>235.0858456375854</v>
+        <v>235.0863880760648</v>
       </c>
     </row>
     <row r="98">
@@ -1494,10 +1494,10 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>302.8513134209892</v>
+        <v>302.8513134207469</v>
       </c>
       <c r="C98" t="n">
-        <v>236.453187385911</v>
+        <v>236.4537298244265</v>
       </c>
     </row>
     <row r="99">
@@ -1505,10 +1505,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>308.6284368297499</v>
+        <v>308.6284368296273</v>
       </c>
       <c r="C99" t="n">
-        <v>236.9495456117669</v>
+        <v>236.9500880502991</v>
       </c>
     </row>
     <row r="100">
@@ -1516,10 +1516,10 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>314.4139735410621</v>
+        <v>314.4139735410603</v>
       </c>
       <c r="C100" t="n">
-        <v>236.5634221464298</v>
+        <v>236.563964584959</v>
       </c>
     </row>
     <row r="101">
@@ -1527,10 +1527,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>314.4139735410625</v>
+        <v>314.4139735410602</v>
       </c>
       <c r="C101" t="n">
-        <v>236.5634221464336</v>
+        <v>236.563964584959</v>
       </c>
     </row>
     <row r="102">
@@ -1538,10 +1538,10 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>316.3352402690714</v>
+        <v>316.3352402690697</v>
       </c>
       <c r="C102" t="n">
-        <v>236.6133151173163</v>
+        <v>236.6138575558425</v>
       </c>
     </row>
     <row r="103">
@@ -1549,10 +1549,10 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>318.1315608705196</v>
+        <v>318.1315608705183</v>
       </c>
       <c r="C103" t="n">
-        <v>237.2966799141197</v>
+        <v>237.2972223526468</v>
       </c>
     </row>
     <row r="104">
@@ -1560,10 +1560,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>319.6001924468043</v>
+        <v>319.6001924468033</v>
       </c>
       <c r="C104" t="n">
-        <v>238.5363881224645</v>
+        <v>238.5369305609921</v>
       </c>
     </row>
     <row r="105">
@@ -1571,10 +1571,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>320.5753769352968</v>
+        <v>320.5753769352962</v>
       </c>
       <c r="C105" t="n">
-        <v>240.1925192652491</v>
+        <v>240.1930617037773</v>
       </c>
     </row>
     <row r="106">
@@ -1582,10 +1582,10 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>320.5753769352968</v>
+        <v>320.5753769352961</v>
       </c>
       <c r="C106" t="n">
-        <v>240.1925192652491</v>
+        <v>240.1930617037773</v>
       </c>
     </row>
     <row r="107">
@@ -1593,10 +1593,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>322.0751465382229</v>
+        <v>322.0751465382224</v>
       </c>
       <c r="C107" t="n">
-        <v>242.4028833018286</v>
+        <v>242.4034257403567</v>
       </c>
     </row>
     <row r="108">
@@ -1604,10 +1604,10 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>324.4075579293233</v>
+        <v>324.4075579293231</v>
       </c>
       <c r="C108" t="n">
-        <v>243.7047570048927</v>
+        <v>243.7052994434206</v>
       </c>
     </row>
     <row r="109">
@@ -1615,10 +1615,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>327.0761709283345</v>
+        <v>327.0761709283344</v>
       </c>
       <c r="C109" t="n">
-        <v>243.8210441390622</v>
+        <v>243.8215865775898</v>
       </c>
     </row>
     <row r="110">
@@ -1626,10 +1626,10 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>329.5129868008402</v>
+        <v>329.5129868008401</v>
       </c>
       <c r="C110" t="n">
-        <v>242.7269936651037</v>
+        <v>242.727536103631</v>
       </c>
     </row>
     <row r="111">
@@ -1637,10 +1637,10 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>329.5129868008418</v>
+        <v>329.5129868008419</v>
       </c>
       <c r="C111" t="n">
-        <v>242.7269936651019</v>
+        <v>242.7275361036279</v>
       </c>
     </row>
     <row r="112">
@@ -1648,10 +1648,10 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>332.2676186962844</v>
+        <v>332.2676186962856</v>
       </c>
       <c r="C112" t="n">
-        <v>241.5811936118158</v>
+        <v>241.5817360503362</v>
       </c>
     </row>
     <row r="113">
@@ -1659,10 +1659,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>335.2270281596573</v>
+        <v>335.2270281596617</v>
       </c>
       <c r="C113" t="n">
-        <v>241.9590166783427</v>
+        <v>241.9595591168626</v>
       </c>
     </row>
     <row r="114">
@@ -1670,10 +1670,10 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>337.6054306825687</v>
+        <v>337.605430682574</v>
       </c>
       <c r="C114" t="n">
-        <v>243.7601430149747</v>
+        <v>243.7606854534985</v>
       </c>
     </row>
     <row r="115">
@@ -1681,10 +1681,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>338.7713111332486</v>
+        <v>338.7713111332494</v>
       </c>
       <c r="C115" t="n">
-        <v>246.5063362740558</v>
+        <v>246.5068787125851</v>
       </c>
     </row>
     <row r="116">
@@ -1692,10 +1692,10 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>338.7713111332515</v>
+        <v>338.7713111332479</v>
       </c>
       <c r="C116" t="n">
-        <v>246.5063362740592</v>
+        <v>246.5068787125859</v>
       </c>
     </row>
     <row r="117">
@@ -1703,10 +1703,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>339.9371915839309</v>
+        <v>339.9371915839251</v>
       </c>
       <c r="C117" t="n">
-        <v>249.2525295331419</v>
+        <v>249.2530719716741</v>
       </c>
     </row>
     <row r="118">
@@ -1714,10 +1714,10 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>342.3155941068432</v>
+        <v>342.3155941068399</v>
       </c>
       <c r="C118" t="n">
-        <v>251.0536558697749</v>
+        <v>251.0541983083106</v>
       </c>
     </row>
     <row r="119">
@@ -1725,10 +1725,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>345.2750035702173</v>
+        <v>345.2750035702184</v>
       </c>
       <c r="C119" t="n">
-        <v>251.4314789363017</v>
+        <v>251.4320213748362</v>
       </c>
     </row>
     <row r="120">
@@ -1736,10 +1736,10 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>348.0296354656608</v>
+        <v>348.0296354656638</v>
       </c>
       <c r="C120" t="n">
-        <v>250.2856788830141</v>
+        <v>250.2862213215428</v>
       </c>
     </row>
     <row r="121">
@@ -1747,10 +1747,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>348.029635465662</v>
+        <v>348.0296354656625</v>
       </c>
       <c r="C121" t="n">
-        <v>250.2856788830153</v>
+        <v>250.2862213215413</v>
       </c>
     </row>
     <row r="122">
@@ -1758,10 +1758,10 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>350.7842673611063</v>
+        <v>350.7842673611034</v>
       </c>
       <c r="C122" t="n">
-        <v>249.1398788297263</v>
+        <v>249.1404212682497</v>
       </c>
     </row>
     <row r="123">
@@ -1769,10 +1769,10 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>353.7436768244818</v>
+        <v>353.743676824477</v>
       </c>
       <c r="C123" t="n">
-        <v>249.5177018962528</v>
+        <v>249.5182443347745</v>
       </c>
     </row>
     <row r="124">
@@ -1780,10 +1780,10 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>356.1220793473949</v>
+        <v>356.1220793473879</v>
       </c>
       <c r="C124" t="n">
-        <v>251.3188282328869</v>
+        <v>251.319370671408</v>
       </c>
     </row>
     <row r="125">
@@ -1791,10 +1791,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>357.287959798074</v>
+        <v>357.2879597980632</v>
       </c>
       <c r="C125" t="n">
-        <v>254.0650214919713</v>
+        <v>254.0655639304917</v>
       </c>
     </row>
     <row r="126">
@@ -1802,10 +1802,10 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>357.2879597980741</v>
+        <v>357.2879597980589</v>
       </c>
       <c r="C126" t="n">
-        <v>254.0650214919714</v>
+        <v>254.0655639304923</v>
       </c>
     </row>
     <row r="127">
@@ -1813,10 +1813,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>358.2686819066489</v>
+        <v>358.4428983717788</v>
       </c>
       <c r="C127" t="n">
-        <v>256.559973037216</v>
+        <v>256.797674067386</v>
       </c>
     </row>
     <row r="128">
@@ -1824,10 +1824,10 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>360.2680957951271</v>
+        <v>360.799261512463</v>
       </c>
       <c r="C128" t="n">
-        <v>258.3457342670355</v>
+        <v>258.5993015700649</v>
       </c>
     </row>
     <row r="129">
@@ -1835,10 +1835,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>362.8575613445259</v>
+        <v>363.7385941954764</v>
       </c>
       <c r="C129" t="n">
-        <v>259.0394685359329</v>
+        <v>258.9975882604687</v>
       </c>
     </row>
     <row r="130">
@@ -1846,10 +1846,10 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>365.4819414581229</v>
+        <v>366.4894342316952</v>
       </c>
       <c r="C130" t="n">
-        <v>258.4924510894809</v>
+        <v>257.8879991453817</v>
       </c>
     </row>
     <row r="131">
@@ -1857,10 +1857,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>365.481941458123</v>
+        <v>366.4894342316977</v>
       </c>
       <c r="C131" t="n">
-        <v>258.4924510894809</v>
+        <v>257.8879991453851</v>
       </c>
     </row>
     <row r="132">
@@ -1868,10 +1868,10 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>370.5217525196807</v>
+        <v>370.7104934895101</v>
       </c>
       <c r="C132" t="n">
-        <v>256.3165353416308</v>
+        <v>255.2700817377697</v>
       </c>
     </row>
     <row r="133">
@@ -1879,10 +1879,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>375.688747702616</v>
+        <v>375.3221539684166</v>
       </c>
       <c r="C133" t="n">
-        <v>254.4627646822809</v>
+        <v>253.4252455828897</v>
       </c>
     </row>
     <row r="134">
@@ -1890,10 +1890,10 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>380.9623591553462</v>
+        <v>380.184178080645</v>
       </c>
       <c r="C134" t="n">
-        <v>252.9385182705829</v>
+        <v>252.4095909451464</v>
       </c>
     </row>
     <row r="135">
@@ -1901,10 +1901,10 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>386.3215946272842</v>
+        <v>385.1487148436031</v>
       </c>
       <c r="C135" t="n">
-        <v>251.7498635544171</v>
+        <v>252.2540032197371</v>
       </c>
     </row>
     <row r="136">
@@ -1912,10 +1912,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>386.3215946272841</v>
+        <v>385.148714843603</v>
       </c>
       <c r="C136" t="n">
-        <v>251.7498635544171</v>
+        <v>252.2540032197348</v>
       </c>
     </row>
     <row r="137">
@@ -1923,10 +1923,10 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>388.903010197979</v>
+        <v>387.465088800376</v>
       </c>
       <c r="C137" t="n">
-        <v>251.0166719257956</v>
+        <v>252.06690111505</v>
       </c>
     </row>
     <row r="138">
@@ -1934,10 +1934,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>391.3113904422754</v>
+        <v>389.645117339784</v>
       </c>
       <c r="C138" t="n">
-        <v>249.8330415308709</v>
+        <v>251.2618724990613</v>
       </c>
     </row>
     <row r="139">
@@ -1945,10 +1945,10 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>393.4688660581145</v>
+        <v>391.5271638231011</v>
       </c>
       <c r="C139" t="n">
-        <v>248.2372422703227</v>
+        <v>249.8986056360343</v>
       </c>
     </row>
     <row r="140">
@@ -1956,10 +1956,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>395.3056801535722</v>
+        <v>392.9716852755497</v>
       </c>
       <c r="C140" t="n">
-        <v>246.2808705542025</v>
+        <v>248.0781789611558</v>
       </c>
     </row>
     <row r="141">
@@ -1967,10 +1967,10 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>395.3056801535712</v>
+        <v>392.9716852755497</v>
       </c>
       <c r="C141" t="n">
-        <v>246.280870554202</v>
+        <v>248.0781789611559</v>
       </c>
     </row>
     <row r="142">
@@ -1978,10 +1978,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>397.0250757748576</v>
+        <v>394.2124387894901</v>
       </c>
       <c r="C142" t="n">
-        <v>244.1578372843611</v>
+        <v>246.3062325284392</v>
       </c>
     </row>
     <row r="143">
@@ -1989,10 +1989,10 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>398.8151224311533</v>
+        <v>395.7092997770129</v>
       </c>
       <c r="C143" t="n">
-        <v>242.0940241785702</v>
+        <v>244.7446081732225</v>
       </c>
     </row>
     <row r="144">
@@ -2000,10 +2000,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>400.6737818431325</v>
+        <v>397.4271355987638</v>
       </c>
       <c r="C144" t="n">
-        <v>240.0917812468532</v>
+        <v>243.4299585878642</v>
       </c>
     </row>
     <row r="145">
@@ -2011,10 +2011,10 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>402.5989376039186</v>
+        <v>399.325627142348</v>
       </c>
       <c r="C145" t="n">
-        <v>238.1533883908867</v>
+        <v>242.393139750404</v>
       </c>
     </row>
     <row r="146">
@@ -2022,10 +2022,10 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>402.5989376039186</v>
+        <v>399.3256271423481</v>
       </c>
       <c r="C146" t="n">
-        <v>238.1533883908866</v>
+        <v>242.393139750404</v>
       </c>
     </row>
     <row r="147">
@@ -2033,10 +2033,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>404.2940026436632</v>
+        <v>401.2055405152622</v>
       </c>
       <c r="C147" t="n">
-        <v>236.7369294512386</v>
+        <v>241.2249475113314</v>
       </c>
     </row>
     <row r="148">
@@ -2044,10 +2044,10 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>405.5564690835571</v>
+        <v>402.7128252775406</v>
       </c>
       <c r="C148" t="n">
-        <v>234.9242574166953</v>
+        <v>239.6041945867639</v>
       </c>
     </row>
     <row r="149">
@@ -2055,10 +2055,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>406.2973034247551</v>
+        <v>403.7417404414549</v>
       </c>
       <c r="C149" t="n">
-        <v>232.8432081872019</v>
+        <v>237.644582129527</v>
       </c>
     </row>
     <row r="150">
@@ -2066,10 +2066,10 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>406.4642594677723</v>
+        <v>404.2201042212908</v>
       </c>
       <c r="C150" t="n">
-        <v>230.6405445505171</v>
+        <v>235.4835834041151</v>
       </c>
     </row>
     <row r="151">
@@ -2077,10 +2077,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>406.4642594677723</v>
+        <v>404.2201042212907</v>
       </c>
       <c r="C151" t="n">
-        <v>230.640544550517</v>
+        <v>235.4835834041151</v>
       </c>
     </row>
     <row r="152">
@@ -2088,10 +2088,10 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>406.5073253402839</v>
+        <v>404.5680455083793</v>
       </c>
       <c r="C152" t="n">
-        <v>228.5719081559049</v>
+        <v>233.3510757805814</v>
       </c>
     </row>
     <row r="153">
@@ -2099,10 +2099,10 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>406.8726424442851</v>
+        <v>405.23778155816</v>
       </c>
       <c r="C153" t="n">
-        <v>226.5353290103735</v>
+        <v>231.2967862373781</v>
       </c>
     </row>
     <row r="154">
@@ -2110,10 +2110,10 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>407.5512616798696</v>
+        <v>406.2135797968274</v>
       </c>
       <c r="C154" t="n">
-        <v>224.5806967852264</v>
+        <v>229.3689714897678</v>
       </c>
     </row>
     <row r="155">
@@ -2121,10 +2121,10 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>408.5265590475835</v>
+        <v>407.4725180331488</v>
       </c>
       <c r="C155" t="n">
-        <v>222.7558937144762</v>
+        <v>227.6129172705541</v>
       </c>
     </row>
     <row r="156">
@@ -2132,10 +2132,10 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>408.5265590475835</v>
+        <v>407.4725180331487</v>
       </c>
       <c r="C156" t="n">
-        <v>222.7558937144762</v>
+        <v>227.6129172705541</v>
       </c>
     </row>
     <row r="157">
@@ -2143,10 +2143,10 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>409.1386891910228</v>
+        <v>408.6591290968117</v>
       </c>
       <c r="C157" t="n">
-        <v>221.4752622902939</v>
+        <v>225.744719948345</v>
       </c>
     </row>
     <row r="158">
@@ -2154,10 +2154,10 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>409.4197128742402</v>
+        <v>409.3136631379036</v>
       </c>
       <c r="C158" t="n">
-        <v>220.0839514527809</v>
+        <v>223.6305316312435</v>
       </c>
     </row>
     <row r="159">
@@ -2165,10 +2165,10 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>409.352629440547</v>
+        <v>409.3902034839506</v>
       </c>
       <c r="C159" t="n">
-        <v>218.6661291895778</v>
+        <v>221.4186662134245</v>
       </c>
     </row>
     <row r="160">
@@ -2176,10 +2176,10 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>408.9414971330517</v>
+        <v>408.883380699935</v>
       </c>
       <c r="C160" t="n">
-        <v>217.3075673091897</v>
+        <v>219.2642898032493</v>
       </c>
     </row>
     <row r="161">
@@ -2187,10 +2187,10 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>408.9414971330517</v>
+        <v>408.8833806999351</v>
       </c>
       <c r="C161" t="n">
-        <v>217.3075673091897</v>
+        <v>219.2642898032494</v>
       </c>
     </row>
     <row r="162">
@@ -2198,10 +2198,10 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>408.3827680908104</v>
+        <v>408.2713983353977</v>
       </c>
       <c r="C162" t="n">
-        <v>215.6974595505476</v>
+        <v>217.1920671138949</v>
       </c>
     </row>
     <row r="163">
@@ -2209,10 +2209,10 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>408.0982459905202</v>
+        <v>407.9832731655285</v>
       </c>
       <c r="C163" t="n">
-        <v>214.0170809290669</v>
+        <v>215.0506626272861</v>
       </c>
     </row>
     <row r="164">
@@ -2220,10 +2220,10 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>408.0957797031296</v>
+        <v>408.0257734666706</v>
       </c>
       <c r="C164" t="n">
-        <v>212.3127866309747</v>
+        <v>212.890379540933</v>
       </c>
     </row>
     <row r="165">
@@ -2231,10 +2231,10 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>408.3754372640263</v>
+        <v>408.3979008748734</v>
       </c>
       <c r="C165" t="n">
-        <v>210.6315915840761</v>
+        <v>210.7619645248132</v>
       </c>
     </row>
     <row r="166">
@@ -2242,10 +2242,10 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>408.3754372640263</v>
+        <v>408.3979008748732</v>
       </c>
       <c r="C166" t="n">
-        <v>210.6315915840761</v>
+        <v>210.7619645248132</v>
       </c>
     </row>
     <row r="167">
@@ -2253,10 +2253,10 @@
         <v>166</v>
       </c>
       <c r="B167" t="n">
-        <v>408.6243051159341</v>
+        <v>408.6545882396246</v>
       </c>
       <c r="C167" t="n">
-        <v>208.5082689572351</v>
+        <v>208.602072866886</v>
       </c>
     </row>
     <row r="168">
@@ -2264,10 +2264,10 @@
         <v>167</v>
       </c>
       <c r="B168" t="n">
-        <v>408.3134351766885</v>
+        <v>408.3408847627744</v>
       </c>
       <c r="C168" t="n">
-        <v>206.393134430487</v>
+        <v>206.4497228707612</v>
       </c>
     </row>
     <row r="169">
@@ -2275,10 +2275,10 @@
         <v>168</v>
       </c>
       <c r="B169" t="n">
-        <v>407.464142353856</v>
+        <v>407.4783671688679</v>
       </c>
       <c r="C169" t="n">
-        <v>204.43121295233</v>
+        <v>204.4529545373264</v>
       </c>
     </row>
     <row r="170">
@@ -2286,10 +2286,10 @@
         <v>169</v>
       </c>
       <c r="B170" t="n">
-        <v>406.1346587108509</v>
+        <v>406.1263599662783</v>
       </c>
       <c r="C170" t="n">
-        <v>202.757024364282</v>
+        <v>202.749106861813</v>
       </c>
     </row>
     <row r="171">
@@ -2297,10 +2297,10 @@
         <v>170</v>
       </c>
       <c r="B171" t="n">
-        <v>406.1346587108509</v>
+        <v>406.1263599662784</v>
       </c>
       <c r="C171" t="n">
-        <v>202.7570243642818</v>
+        <v>202.749106861813</v>
       </c>
     </row>
     <row r="172">
@@ -2308,10 +2308,10 @@
         <v>171</v>
       </c>
       <c r="B172" t="n">
-        <v>403.2976201694007</v>
+        <v>403.2918284639377</v>
       </c>
       <c r="C172" t="n">
-        <v>199.8407610069574</v>
+        <v>199.8346014070189</v>
       </c>
     </row>
     <row r="173">
@@ -2319,10 +2319,10 @@
         <v>172</v>
       </c>
       <c r="B173" t="n">
-        <v>400.6455527077763</v>
+        <v>400.642014504364</v>
       </c>
       <c r="C173" t="n">
-        <v>196.7553245979642</v>
+        <v>196.7511947093167</v>
       </c>
     </row>
     <row r="174">
@@ -2330,10 +2330,10 @@
         <v>173</v>
       </c>
       <c r="B174" t="n">
-        <v>398.1885231242821</v>
+        <v>398.1869614641168</v>
       </c>
       <c r="C174" t="n">
-        <v>193.5124269306331</v>
+        <v>193.5105735569202</v>
       </c>
     </row>
     <row r="175">
@@ -2341,10 +2341,10 @@
         <v>174</v>
       </c>
       <c r="B175" t="n">
-        <v>395.9358578865146</v>
+        <v>395.9359745331201</v>
       </c>
       <c r="C175" t="n">
-        <v>190.1243774945266</v>
+        <v>190.1250206153362</v>
       </c>
     </row>
     <row r="176">
@@ -2352,10 +2352,10 @@
         <v>175</v>
       </c>
       <c r="B176" t="n">
-        <v>395.9358578865143</v>
+        <v>395.9359745331204</v>
       </c>
       <c r="C176" t="n">
-        <v>190.1243774945269</v>
+        <v>190.1250206153361</v>
       </c>
     </row>
     <row r="177">
@@ -2363,10 +2363,10 @@
         <v>176</v>
       </c>
       <c r="B177" t="n">
-        <v>394.1126121664821</v>
+        <v>394.1126235715064</v>
       </c>
       <c r="C177" t="n">
-        <v>187.6704062734384</v>
+        <v>187.6709830880134</v>
       </c>
     </row>
     <row r="178">
@@ -2374,10 +2374,10 @@
         <v>177</v>
       </c>
       <c r="B178" t="n">
-        <v>391.9087982179028</v>
+        <v>391.9087131595023</v>
       </c>
       <c r="C178" t="n">
-        <v>185.5515849526107</v>
+        <v>185.552094744899</v>
       </c>
     </row>
     <row r="179">
@@ -2385,10 +2385,10 @@
         <v>178</v>
       </c>
       <c r="B179" t="n">
-        <v>389.3850532617316</v>
+        <v>389.38487688256</v>
       </c>
       <c r="C179" t="n">
-        <v>183.826212208608</v>
+        <v>183.8266500596317</v>
       </c>
     </row>
     <row r="180">
@@ -2396,10 +2396,10 @@
         <v>179</v>
       </c>
       <c r="B180" t="n">
-        <v>386.6108173160975</v>
+        <v>386.6105500687817</v>
       </c>
       <c r="C180" t="n">
-        <v>182.5417611089167</v>
+        <v>182.5421191549522</v>
       </c>
     </row>
     <row r="181">
@@ -2407,10 +2407,10 @@
         <v>180</v>
       </c>
       <c r="B181" t="n">
-        <v>386.6108173160979</v>
+        <v>386.6105500687812</v>
       </c>
       <c r="C181" t="n">
-        <v>182.5417611089152</v>
+        <v>182.5421191549527</v>
       </c>
     </row>
     <row r="182">
@@ -2418,10 +2418,10 @@
         <v>181</v>
       </c>
       <c r="B182" t="n">
-        <v>377.9711077551399</v>
+        <v>377.5969836765634</v>
       </c>
       <c r="C182" t="n">
-        <v>179.0684248580662</v>
+        <v>178.9183428176686</v>
       </c>
     </row>
     <row r="183">
@@ -2429,10 +2429,10 @@
         <v>182</v>
       </c>
       <c r="B183" t="n">
-        <v>369.568607016039</v>
+        <v>368.8308833446679</v>
       </c>
       <c r="C183" t="n">
-        <v>175.0551185728968</v>
+        <v>174.7312651947052</v>
       </c>
     </row>
     <row r="184">
@@ -2440,10 +2440,10 @@
         <v>183</v>
       </c>
       <c r="B184" t="n">
-        <v>361.4370221113144</v>
+        <v>360.3474103767045</v>
       </c>
       <c r="C184" t="n">
-        <v>170.5179418134543</v>
+        <v>169.9976808813744</v>
       </c>
     </row>
     <row r="185">
@@ -2451,10 +2451,10 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>353.6089732623374</v>
+        <v>352.1805924426056</v>
       </c>
       <c r="C185" t="n">
-        <v>165.4750956699358</v>
+        <v>164.7365765409472</v>
       </c>
     </row>
     <row r="186">
@@ -2462,10 +2462,10 @@
         <v>185</v>
       </c>
       <c r="B186" t="n">
-        <v>353.6089732623323</v>
+        <v>352.1805924426058</v>
       </c>
       <c r="C186" t="n">
-        <v>165.4750956699353</v>
+        <v>164.7365765409473</v>
       </c>
     </row>
     <row r="187">
@@ -2473,10 +2473,10 @@
         <v>186</v>
       </c>
       <c r="B187" t="n">
-        <v>334.9997213548114</v>
+        <v>335.3588946156825</v>
       </c>
       <c r="C187" t="n">
-        <v>152.635279918523</v>
+        <v>153.1301185383912</v>
       </c>
     </row>
     <row r="188">
@@ -2484,10 +2484,10 @@
         <v>187</v>
       </c>
       <c r="B188" t="n">
-        <v>334.9997213548114</v>
+        <v>335.3588946156825</v>
       </c>
       <c r="C188" t="n">
-        <v>152.635279918523</v>
+        <v>153.1301185383911</v>
       </c>
     </row>
     <row r="189">
@@ -2495,10 +2495,10 @@
         <v>188</v>
       </c>
       <c r="B189" t="n">
-        <v>332.4108970925137</v>
+        <v>332.6530673697296</v>
       </c>
       <c r="C189" t="n">
-        <v>150.4030819664633</v>
+        <v>150.7997827614826</v>
       </c>
     </row>
     <row r="190">
@@ -2506,10 +2506,10 @@
         <v>189</v>
       </c>
       <c r="B190" t="n">
-        <v>330.3584418359121</v>
+        <v>330.5039391409719</v>
       </c>
       <c r="C190" t="n">
-        <v>147.6695592982036</v>
+        <v>147.9479037713363</v>
       </c>
     </row>
     <row r="191">
@@ -2517,10 +2517,10 @@
         <v>190</v>
       </c>
       <c r="B191" t="n">
-        <v>328.9370357157478</v>
+        <v>329.0095828941451</v>
       </c>
       <c r="C191" t="n">
-        <v>144.5608098068807</v>
+        <v>144.7046237455521</v>
       </c>
     </row>
     <row r="192">
@@ -2528,10 +2528,10 @@
         <v>191</v>
       </c>
       <c r="B192" t="n">
-        <v>328.2122484524133</v>
+        <v>328.2381918368658</v>
       </c>
       <c r="C192" t="n">
-        <v>141.220240666577</v>
+        <v>141.2179459923276</v>
       </c>
     </row>
     <row r="193">
@@ -2539,10 +2539,10 @@
         <v>192</v>
       </c>
       <c r="B193" t="n">
-        <v>328.2122484524133</v>
+        <v>328.2381918368658</v>
       </c>
       <c r="C193" t="n">
-        <v>141.220240666577</v>
+        <v>141.2179459923276</v>
       </c>
     </row>
     <row r="194">
@@ -2550,10 +2550,10 @@
         <v>193</v>
       </c>
       <c r="B194" t="n">
-        <v>327.2729708125624</v>
+        <v>327.288452951187</v>
       </c>
       <c r="C194" t="n">
-        <v>138.5916803668457</v>
+        <v>138.5925849876285</v>
       </c>
     </row>
     <row r="195">
@@ -2561,10 +2561,10 @@
         <v>194</v>
       </c>
       <c r="B195" t="n">
-        <v>325.2369179194757</v>
+        <v>325.2473984664559</v>
       </c>
       <c r="C195" t="n">
-        <v>136.682214381131</v>
+        <v>136.6876910414141</v>
       </c>
     </row>
     <row r="196">
@@ -2572,10 +2572,10 @@
         <v>195</v>
       </c>
       <c r="B196" t="n">
-        <v>322.5535544930612</v>
+        <v>322.5628158028262</v>
       </c>
       <c r="C196" t="n">
-        <v>135.9133629937817</v>
+        <v>135.9211792814887</v>
       </c>
     </row>
     <row r="197">
@@ -2583,10 +2583,10 @@
         <v>196</v>
       </c>
       <c r="B197" t="n">
-        <v>319.8152409749163</v>
+        <v>319.8236761779352</v>
       </c>
       <c r="C197" t="n">
-        <v>136.4548524307908</v>
+        <v>136.4612149019038</v>
       </c>
     </row>
     <row r="198">
@@ -2594,10 +2594,10 @@
         <v>197</v>
       </c>
       <c r="B198" t="n">
-        <v>319.8152409749163</v>
+        <v>319.8236761779347</v>
       </c>
       <c r="C198" t="n">
-        <v>136.4548524307907</v>
+        <v>136.4612149019028</v>
       </c>
     </row>
     <row r="199">
@@ -2605,10 +2605,10 @@
         <v>198</v>
       </c>
       <c r="B199" t="n">
-        <v>317.4175487452189</v>
+        <v>317.4231717147758</v>
       </c>
       <c r="C199" t="n">
-        <v>136.9972074842253</v>
+        <v>137.0016485444542</v>
       </c>
     </row>
     <row r="200">
@@ -2616,10 +2616,10 @@
         <v>199</v>
       </c>
       <c r="B200" t="n">
-        <v>315.0070046027007</v>
+        <v>315.010550712655</v>
       </c>
       <c r="C200" t="n">
-        <v>136.5151763967332</v>
+        <v>136.5181714511258</v>
       </c>
     </row>
     <row r="201">
@@ -2627,10 +2627,10 @@
         <v>200</v>
       </c>
       <c r="B201" t="n">
-        <v>313.0022600940196</v>
+        <v>313.0036401983863</v>
       </c>
       <c r="C201" t="n">
-        <v>135.0924759759663</v>
+        <v>135.0945140529554</v>
       </c>
     </row>
     <row r="202">
@@ -2638,10 +2638,10 @@
         <v>201</v>
       </c>
       <c r="B202" t="n">
-        <v>311.7514894651515</v>
+        <v>311.75000468895</v>
       </c>
       <c r="C202" t="n">
-        <v>132.976193890256</v>
+        <v>132.9772308387567</v>
       </c>
     </row>
     <row r="203">
@@ -2649,10 +2649,10 @@
         <v>202</v>
       </c>
       <c r="B203" t="n">
-        <v>311.7514894651515</v>
+        <v>311.7500046889527</v>
       </c>
       <c r="C203" t="n">
-        <v>132.976193890256</v>
+        <v>132.9772308387557</v>
       </c>
     </row>
     <row r="204">
@@ -2660,10 +2660,10 @@
         <v>203</v>
       </c>
       <c r="B204" t="n">
-        <v>310.8085321212725</v>
+        <v>310.8061176662985</v>
       </c>
       <c r="C204" t="n">
-        <v>130.8939811827338</v>
+        <v>130.8966703391748</v>
       </c>
     </row>
     <row r="205">
@@ -2671,10 +2671,10 @@
         <v>204</v>
       </c>
       <c r="B205" t="n">
-        <v>309.4657006671954</v>
+        <v>309.4642898510037</v>
       </c>
       <c r="C205" t="n">
-        <v>129.0442293081074</v>
+        <v>129.0475752042364</v>
       </c>
     </row>
     <row r="206">
@@ -2682,10 +2682,10 @@
         <v>205</v>
       </c>
       <c r="B206" t="n">
-        <v>307.777979597194</v>
+        <v>307.7790033363428</v>
       </c>
       <c r="C206" t="n">
-        <v>127.5026794705687</v>
+        <v>127.5050240486979</v>
       </c>
     </row>
     <row r="207">
@@ -2693,10 +2693,10 @@
         <v>206</v>
       </c>
       <c r="B207" t="n">
-        <v>305.8144754914184</v>
+        <v>305.8186856329391</v>
       </c>
       <c r="C207" t="n">
-        <v>126.3324530231045</v>
+        <v>126.3316489144491</v>
       </c>
     </row>
     <row r="208">
@@ -2704,10 +2704,10 @@
         <v>207</v>
       </c>
       <c r="B208" t="n">
-        <v>305.8144754914182</v>
+        <v>305.8186856329397</v>
       </c>
       <c r="C208" t="n">
-        <v>126.3324530231045</v>
+        <v>126.3316489144483</v>
       </c>
     </row>
     <row r="209">
@@ -2715,10 +2715,10 @@
         <v>208</v>
       </c>
       <c r="B209" t="n">
-        <v>298.3493862428205</v>
+        <v>297.7103628575971</v>
       </c>
       <c r="C209" t="n">
-        <v>124.0944350746251</v>
+        <v>123.9871210317564</v>
       </c>
     </row>
     <row r="210">
@@ -2726,10 +2726,10 @@
         <v>209</v>
       </c>
       <c r="B210" t="n">
-        <v>290.5560474571024</v>
+        <v>289.2743286740786</v>
       </c>
       <c r="C210" t="n">
-        <v>124.0820901052206</v>
+        <v>124.2610488988453</v>
       </c>
     </row>
     <row r="211">
@@ -2737,10 +2737,10 @@
         <v>210</v>
       </c>
       <c r="B211" t="n">
-        <v>283.0839054637109</v>
+        <v>281.3351850807477</v>
       </c>
       <c r="C211" t="n">
-        <v>126.2964468646076</v>
+        <v>127.1266567272706</v>
       </c>
     </row>
     <row r="212">
@@ -2748,10 +2748,10 @@
         <v>211</v>
       </c>
       <c r="B212" t="n">
-        <v>276.5556401337697</v>
+        <v>274.6689642190037</v>
       </c>
       <c r="C212" t="n">
-        <v>130.5529752163438</v>
+        <v>132.303838262074</v>
       </c>
     </row>
     <row r="213">
@@ -2759,10 +2759,10 @@
         <v>212</v>
       </c>
       <c r="B213" t="n">
-        <v>276.5556401337696</v>
+        <v>274.6689642190028</v>
       </c>
       <c r="C213" t="n">
-        <v>130.5529752163438</v>
+        <v>132.3038382620731</v>
       </c>
     </row>
     <row r="214">
@@ -2770,10 +2770,10 @@
         <v>213</v>
       </c>
       <c r="B214" t="n">
-        <v>271.0476115486424</v>
+        <v>268.5131890505564</v>
       </c>
       <c r="C214" t="n">
-        <v>134.9364618021081</v>
+        <v>137.628607410812</v>
       </c>
     </row>
     <row r="215">
@@ -2781,10 +2781,10 @@
         <v>214</v>
       </c>
       <c r="B215" t="n">
-        <v>265.1261480811992</v>
+        <v>261.389303512937</v>
       </c>
       <c r="C215" t="n">
-        <v>138.742983041493</v>
+        <v>141.5652289647235</v>
       </c>
     </row>
     <row r="216">
@@ -2792,10 +2792,10 @@
         <v>215</v>
       </c>
       <c r="B216" t="n">
-        <v>258.8514542866359</v>
+        <v>253.6053102888433</v>
       </c>
       <c r="C216" t="n">
-        <v>141.9338373670025</v>
+        <v>143.9435022667406</v>
       </c>
     </row>
     <row r="217">
@@ -2803,10 +2803,10 @@
         <v>216</v>
       </c>
       <c r="B217" t="n">
-        <v>252.2873260746917</v>
+        <v>245.497751955001</v>
       </c>
       <c r="C217" t="n">
-        <v>144.4765828043816</v>
+        <v>144.6606021727275</v>
       </c>
     </row>
     <row r="218">
@@ -2814,10 +2814,10 @@
         <v>217</v>
       </c>
       <c r="B218" t="n">
-        <v>252.2873260746917</v>
+        <v>245.4977519550009</v>
       </c>
       <c r="C218" t="n">
-        <v>144.4765828043815</v>
+        <v>144.6606021727304</v>
       </c>
     </row>
     <row r="219">
@@ -2825,10 +2825,10 @@
         <v>218</v>
       </c>
       <c r="B219" t="n">
-        <v>247.5532143423943</v>
+        <v>242.3081922696092</v>
       </c>
       <c r="C219" t="n">
-        <v>145.2789486019254</v>
+        <v>144.2447420257101</v>
       </c>
     </row>
     <row r="220">
@@ -2836,10 +2836,10 @@
         <v>219</v>
       </c>
       <c r="B220" t="n">
-        <v>242.795016405529</v>
+        <v>239.2945335790782</v>
       </c>
       <c r="C220" t="n">
-        <v>144.6346216968882</v>
+        <v>143.1204235897039</v>
       </c>
     </row>
     <row r="221">
@@ -2847,10 +2847,10 @@
         <v>220</v>
       </c>
       <c r="B221" t="n">
-        <v>238.4447871637783</v>
+        <v>236.6119861303382</v>
       </c>
       <c r="C221" t="n">
-        <v>142.602108397753</v>
+        <v>141.345551810162</v>
       </c>
     </row>
     <row r="222">
@@ -2858,10 +2858,10 @@
         <v>221</v>
       </c>
       <c r="B222" t="n">
-        <v>234.8975370567203</v>
+        <v>234.3987071915723</v>
       </c>
       <c r="C222" t="n">
-        <v>139.3659654088044</v>
+        <v>139.0115366028911</v>
       </c>
     </row>
     <row r="223">
@@ -2869,10 +2869,10 @@
         <v>222</v>
       </c>
       <c r="B223" t="n">
-        <v>234.8975370567169</v>
+        <v>234.3987071915738</v>
       </c>
       <c r="C223" t="n">
-        <v>139.3659654088072</v>
+        <v>139.0115366028905</v>
       </c>
     </row>
     <row r="224">
@@ -2880,10 +2880,10 @@
         <v>223</v>
       </c>
       <c r="B224" t="n">
-        <v>233.4230517247506</v>
+        <v>232.9629461408455</v>
       </c>
       <c r="C224" t="n">
-        <v>137.7770773480783</v>
+        <v>137.3809074736557</v>
       </c>
     </row>
     <row r="225">
@@ -2891,10 +2891,10 @@
         <v>224</v>
       </c>
       <c r="B225" t="n">
-        <v>231.7465272106608</v>
+        <v>231.2946185462335</v>
       </c>
       <c r="C225" t="n">
-        <v>136.4030548528597</v>
+        <v>135.9891301247403</v>
       </c>
     </row>
     <row r="226">
@@ -2902,10 +2902,10 @@
         <v>225</v>
       </c>
       <c r="B226" t="n">
-        <v>229.8990011992936</v>
+        <v>229.433003932268</v>
       </c>
       <c r="C226" t="n">
-        <v>135.2693353544684</v>
+        <v>134.8689729121279</v>
       </c>
     </row>
     <row r="227">
@@ -2913,10 +2913,10 @@
         <v>226</v>
       </c>
       <c r="B227" t="n">
-        <v>227.9146771452387</v>
+        <v>227.4219326216812</v>
       </c>
       <c r="C227" t="n">
-        <v>134.3969075281068</v>
+        <v>134.0468090989907</v>
       </c>
     </row>
     <row r="228">
@@ -2924,10 +2924,10 @@
         <v>227</v>
       </c>
       <c r="B228" t="n">
-        <v>227.9146771452403</v>
+        <v>227.4219326216808</v>
       </c>
       <c r="C228" t="n">
-        <v>134.3969075281024</v>
+        <v>134.046809098992</v>
       </c>
     </row>
     <row r="229">
@@ -2935,10 +2935,10 @@
         <v>228</v>
       </c>
       <c r="B229" t="n">
-        <v>225.9301320406837</v>
+        <v>225.4200016026945</v>
       </c>
       <c r="C229" t="n">
-        <v>133.5243825146868</v>
+        <v>133.2283820091405</v>
       </c>
     </row>
     <row r="230">
@@ -2946,10 +2946,10 @@
         <v>229</v>
       </c>
       <c r="B230" t="n">
-        <v>224.0824002178963</v>
+        <v>223.5668480016875</v>
       </c>
       <c r="C230" t="n">
-        <v>132.3905367217705</v>
+        <v>132.1133158957385</v>
       </c>
     </row>
     <row r="231">
@@ -2957,10 +2957,10 @@
         <v>230</v>
       </c>
       <c r="B231" t="n">
-        <v>222.4056889416775</v>
+        <v>221.9061029331747</v>
       </c>
       <c r="C231" t="n">
-        <v>131.0163611626603</v>
+        <v>130.7278641558381</v>
       </c>
     </row>
     <row r="232">
@@ -2968,10 +2968,10 @@
         <v>231</v>
       </c>
       <c r="B232" t="n">
-        <v>220.9310393544214</v>
+        <v>220.4768673967846</v>
       </c>
       <c r="C232" t="n">
-        <v>129.4272961023619</v>
+        <v>129.1046462136929</v>
       </c>
     </row>
     <row r="233">
@@ -2979,10 +2979,10 @@
         <v>232</v>
       </c>
       <c r="B233" t="n">
-        <v>220.9310393544183</v>
+        <v>220.4768673967846</v>
       </c>
       <c r="C233" t="n">
-        <v>129.4272961023645</v>
+        <v>129.104646213693</v>
       </c>
     </row>
     <row r="234">
@@ -2990,10 +2990,10 @@
         <v>233</v>
       </c>
       <c r="B234" t="n">
-        <v>219.4558384783725</v>
+        <v>219.0863868839606</v>
       </c>
       <c r="C234" t="n">
-        <v>127.8376369797469</v>
+        <v>127.5254433047592</v>
       </c>
     </row>
     <row r="235">
@@ -3001,10 +3001,10 @@
         <v>234</v>
       </c>
       <c r="B235" t="n">
-        <v>217.778500373829</v>
+        <v>217.4706744308768</v>
       </c>
       <c r="C235" t="n">
-        <v>126.462947693452</v>
+        <v>126.1775593508973</v>
       </c>
     </row>
     <row r="236">
@@ -3012,10 +3012,10 @@
         <v>235</v>
       </c>
       <c r="B236" t="n">
-        <v>215.9300777877245</v>
+        <v>215.6677707779367</v>
       </c>
       <c r="C236" t="n">
-        <v>125.3286780191741</v>
+        <v>125.092729270957</v>
       </c>
     </row>
     <row r="237">
@@ -3023,10 +3023,10 @@
         <v>236</v>
       </c>
       <c r="B237" t="n">
-        <v>213.9447907730366</v>
+        <v>213.7201239422381</v>
       </c>
       <c r="C237" t="n">
-        <v>124.4558268175829</v>
+        <v>124.2964945772129</v>
       </c>
     </row>
     <row r="238">
@@ -3034,10 +3034,10 @@
         <v>237</v>
       </c>
       <c r="B238" t="n">
-        <v>213.9447907730367</v>
+        <v>213.720123942239</v>
       </c>
       <c r="C238" t="n">
-        <v>124.4558268175823</v>
+        <v>124.2964945772103</v>
       </c>
     </row>
     <row r="239">
@@ -3045,10 +3045,10 @@
         <v>238</v>
       </c>
       <c r="B239" t="n">
-        <v>211.9569953780095</v>
+        <v>211.9717201747146</v>
       </c>
       <c r="C239" t="n">
-        <v>123.5818727816015</v>
+        <v>123.581714200779</v>
       </c>
     </row>
     <row r="240">
@@ -3056,10 +3056,10 @@
         <v>239</v>
       </c>
       <c r="B240" t="n">
-        <v>210.1062373377167</v>
+        <v>210.3532524517646</v>
       </c>
       <c r="C240" t="n">
-        <v>122.4461699746182</v>
+        <v>122.6078615678857</v>
       </c>
     </row>
     <row r="241">
@@ -3067,10 +3067,10 @@
         <v>240</v>
       </c>
       <c r="B241" t="n">
-        <v>208.4267799416589</v>
+        <v>208.902826384559</v>
       </c>
       <c r="C241" t="n">
-        <v>121.0697437890473</v>
+        <v>121.3978653098771</v>
       </c>
     </row>
     <row r="242">
@@ -3078,10 +3078,10 @@
         <v>241</v>
       </c>
       <c r="B242" t="n">
-        <v>206.9497151714525</v>
+        <v>207.6545911692569</v>
       </c>
       <c r="C242" t="n">
-        <v>119.4780761559928</v>
+        <v>119.9802138830079</v>
       </c>
     </row>
     <row r="243">
@@ -3089,10 +3089,10 @@
         <v>242</v>
       </c>
       <c r="B243" t="n">
-        <v>206.9497151714542</v>
+        <v>207.6545911692557</v>
       </c>
       <c r="C243" t="n">
-        <v>119.4780761559915</v>
+        <v>119.9802138830087</v>
       </c>
     </row>
     <row r="244">
@@ -3100,10 +3100,10 @@
         <v>243</v>
       </c>
       <c r="B244" t="n">
-        <v>205.4661905204223</v>
+        <v>206.4760955655499</v>
       </c>
       <c r="C244" t="n">
-        <v>117.879447431297</v>
+        <v>118.6417674478565</v>
       </c>
     </row>
     <row r="245">
@@ -3111,10 +3111,10 @@
         <v>244</v>
       </c>
       <c r="B245" t="n">
-        <v>203.7793880878779</v>
+        <v>205.1067056278623</v>
       </c>
       <c r="C245" t="n">
-        <v>116.4970015035298</v>
+        <v>117.499374369146</v>
       </c>
     </row>
     <row r="246">
@@ -3122,10 +3122,10 @@
         <v>245</v>
       </c>
       <c r="B246" t="n">
-        <v>201.9205358349152</v>
+        <v>203.5786626173349</v>
       </c>
       <c r="C246" t="n">
-        <v>115.3563317479506</v>
+        <v>116.5799314368743</v>
       </c>
     </row>
     <row r="247">
@@ -3133,10 +3133,10 @@
         <v>246</v>
       </c>
       <c r="B247" t="n">
-        <v>199.9240469000944</v>
+        <v>201.9279431629639</v>
       </c>
       <c r="C247" t="n">
-        <v>114.4785555106463</v>
+        <v>115.9050862467108</v>
       </c>
     </row>
     <row r="248">
@@ -3144,10 +3144,10 @@
         <v>247</v>
       </c>
       <c r="B248" t="n">
-        <v>199.9240469000948</v>
+        <v>201.9279431629641</v>
       </c>
       <c r="C248" t="n">
-        <v>114.4785555106446</v>
+        <v>115.9050862467109</v>
       </c>
     </row>
     <row r="249">
@@ -3155,10 +3155,10 @@
         <v>248</v>
       </c>
       <c r="B249" t="n">
-        <v>197.0110966768588</v>
+        <v>199.8889546119616</v>
       </c>
       <c r="C249" t="n">
-        <v>113.0880777589737</v>
+        <v>115.055247994941</v>
       </c>
     </row>
     <row r="250">
@@ -3166,10 +3166,10 @@
         <v>249</v>
       </c>
       <c r="B250" t="n">
-        <v>194.429434115362</v>
+        <v>198.0198562959686</v>
       </c>
       <c r="C250" t="n">
-        <v>111.1506243274021</v>
+        <v>113.8778904237492</v>
       </c>
     </row>
     <row r="251">
@@ -3177,10 +3177,10 @@
         <v>250</v>
       </c>
       <c r="B251" t="n">
-        <v>192.2803893830589</v>
+        <v>196.3727914555437</v>
       </c>
       <c r="C251" t="n">
-        <v>108.7422401970145</v>
+        <v>112.4058589102527</v>
       </c>
     </row>
     <row r="252">
@@ -3188,10 +3188,10 @@
         <v>251</v>
       </c>
       <c r="B252" t="n">
-        <v>190.6483124123684</v>
+        <v>194.9937091440112</v>
       </c>
       <c r="C252" t="n">
-        <v>105.9574543627564</v>
+        <v>110.6802195089557</v>
       </c>
     </row>
     <row r="253">
@@ -3199,10 +3199,10 @@
         <v>252</v>
       </c>
       <c r="B253" t="n">
-        <v>190.6483124123667</v>
+        <v>194.993709144009</v>
       </c>
       <c r="C253" t="n">
-        <v>105.9574543627572</v>
+        <v>110.680219508957</v>
       </c>
     </row>
     <row r="254">
@@ -3210,10 +3210,10 @@
         <v>253</v>
       </c>
       <c r="B254" t="n">
-        <v>189.4454221178581</v>
+        <v>193.4680660929153</v>
       </c>
       <c r="C254" t="n">
-        <v>104.3994917050049</v>
+        <v>108.9402241985627</v>
       </c>
     </row>
     <row r="255">
@@ -3221,10 +3221,10 @@
         <v>254</v>
       </c>
       <c r="B255" t="n">
-        <v>187.6818203579633</v>
+        <v>191.5483741566957</v>
       </c>
       <c r="C255" t="n">
-        <v>103.5254770963913</v>
+        <v>107.647957480908</v>
       </c>
     </row>
     <row r="256">
@@ -3232,10 +3232,10 @@
         <v>255</v>
       </c>
       <c r="B256" t="n">
-        <v>185.7135704866428</v>
+        <v>189.3621554046352</v>
       </c>
       <c r="C256" t="n">
-        <v>103.5118702003338</v>
+        <v>106.8892625701014</v>
       </c>
     </row>
     <row r="257">
@@ -3243,10 +3243,10 @@
         <v>256</v>
       </c>
       <c r="B257" t="n">
-        <v>183.9380534016429</v>
+        <v>187.0546368567116</v>
       </c>
       <c r="C257" t="n">
-        <v>104.3614181886471</v>
+        <v>106.7145383573174</v>
       </c>
     </row>
     <row r="258">
@@ -3254,10 +3254,10 @@
         <v>257</v>
       </c>
       <c r="B258" t="n">
-        <v>183.9380534016439</v>
+        <v>187.0546368567115</v>
       </c>
       <c r="C258" t="n">
-        <v>104.3614181886484</v>
+        <v>106.714538357315</v>
       </c>
     </row>
     <row r="259">
@@ -3265,10 +3265,10 @@
         <v>258</v>
       </c>
       <c r="B259" t="n">
-        <v>181.4623226475111</v>
+        <v>183.7041792245355</v>
       </c>
       <c r="C259" t="n">
-        <v>105.1684415114247</v>
+        <v>106.174616167127</v>
       </c>
     </row>
     <row r="260">
@@ -3276,10 +3276,10 @@
         <v>259</v>
       </c>
       <c r="B260" t="n">
-        <v>179.0643622257361</v>
+        <v>180.8778846967925</v>
       </c>
       <c r="C260" t="n">
-        <v>104.1533970660608</v>
+        <v>104.2960152092558</v>
       </c>
     </row>
     <row r="261">
@@ -3287,10 +3287,10 @@
         <v>260</v>
       </c>
       <c r="B261" t="n">
-        <v>177.9204175215368</v>
+        <v>179.0829483618977</v>
       </c>
       <c r="C261" t="n">
-        <v>101.8141835392108</v>
+        <v>101.4158614164631</v>
       </c>
     </row>
     <row r="262">
@@ -3298,10 +3298,10 @@
         <v>261</v>
       </c>
       <c r="B262" t="n">
-        <v>178.5916152603757</v>
+        <v>178.6414820465343</v>
       </c>
       <c r="C262" t="n">
-        <v>99.2982298421326</v>
+        <v>98.05101523738391</v>
       </c>
     </row>
     <row r="263">
@@ -3309,10 +3309,10 @@
         <v>262</v>
       </c>
       <c r="B263" t="n">
-        <v>178.5916152603758</v>
+        <v>178.6414820465343</v>
       </c>
       <c r="C263" t="n">
-        <v>99.29822984213268</v>
+        <v>98.05101523738396</v>
       </c>
     </row>
     <row r="264">
@@ -3320,10 +3320,10 @@
         <v>263</v>
       </c>
       <c r="B264" t="n">
-        <v>179.083444829225</v>
+        <v>178.1119100949609</v>
       </c>
       <c r="C264" t="n">
-        <v>97.15696444796068</v>
+        <v>95.53835090080879</v>
       </c>
     </row>
     <row r="265">
@@ -3331,10 +3331,10 @@
         <v>264</v>
       </c>
       <c r="B265" t="n">
-        <v>177.9171175720073</v>
+        <v>176.2894286345504</v>
       </c>
       <c r="C265" t="n">
-        <v>95.2950851441002</v>
+        <v>93.72934845563356</v>
       </c>
     </row>
     <row r="266">
@@ -3342,10 +3342,10 @@
         <v>265</v>
       </c>
       <c r="B266" t="n">
-        <v>175.7758521778353</v>
+        <v>173.7729023490368</v>
       </c>
       <c r="C266" t="n">
-        <v>94.80325557525096</v>
+        <v>93.21844340133369</v>
       </c>
     </row>
     <row r="267">
@@ -3353,10 +3353,10 @@
         <v>266</v>
       </c>
       <c r="B267" t="n">
-        <v>173.9139728739748</v>
+        <v>171.3892580142584</v>
       </c>
       <c r="C267" t="n">
-        <v>95.96958283246873</v>
+        <v>94.17351837507601</v>
       </c>
     </row>
     <row r="268">
@@ -3364,10 +3364,10 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>173.9139728739751</v>
+        <v>171.3892580142584</v>
       </c>
       <c r="C268" t="n">
-        <v>95.96958283246889</v>
+        <v>94.17351837507594</v>
       </c>
     </row>
     <row r="269">
@@ -3375,10 +3375,10 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>172.4295457735842</v>
+        <v>169.478082552899</v>
       </c>
       <c r="C269" t="n">
-        <v>97.19575768723354</v>
+        <v>95.04268115896869</v>
       </c>
     </row>
     <row r="270">
@@ -3386,10 +3386,10 @@
         <v>269</v>
       </c>
       <c r="B270" t="n">
-        <v>170.5308346494933</v>
+        <v>167.3827296949417</v>
       </c>
       <c r="C270" t="n">
-        <v>97.51501410155502</v>
+        <v>94.91027273908303</v>
       </c>
     </row>
     <row r="271">
@@ -3397,10 +3397,10 @@
         <v>270</v>
       </c>
       <c r="B271" t="n">
-        <v>168.7270263151816</v>
+        <v>165.5961672398764</v>
       </c>
       <c r="C271" t="n">
-        <v>96.84173549362235</v>
+        <v>93.80744447359575</v>
       </c>
     </row>
     <row r="272">
@@ -3408,10 +3408,10 @@
         <v>271</v>
       </c>
       <c r="B272" t="n">
-        <v>167.5018570305899</v>
+        <v>164.5387147337788</v>
       </c>
       <c r="C272" t="n">
-        <v>95.35647833914541</v>
+        <v>91.99365568039119</v>
       </c>
     </row>
     <row r="273">
@@ -3419,10 +3419,10 @@
         <v>272</v>
       </c>
       <c r="B273" t="n">
-        <v>167.5018570305897</v>
+        <v>164.5387147337788</v>
       </c>
       <c r="C273" t="n">
-        <v>95.35647833914537</v>
+        <v>91.99365568039117</v>
       </c>
     </row>
     <row r="274">
@@ -3430,10 +3430,10 @@
         <v>273</v>
       </c>
       <c r="B274" t="n">
-        <v>164.1510781114218</v>
+        <v>162.864744616143</v>
       </c>
       <c r="C274" t="n">
-        <v>89.46383003999085</v>
+        <v>87.92876685051415</v>
       </c>
     </row>
     <row r="275">
@@ -3441,10 +3441,10 @@
         <v>274</v>
       </c>
       <c r="B275" t="n">
-        <v>159.8076033441077</v>
+        <v>160.3600542465559</v>
       </c>
       <c r="C275" t="n">
-        <v>84.25948086950129</v>
+        <v>84.31600844363243</v>
       </c>
     </row>
     <row r="276">
@@ -3452,10 +3452,10 @@
         <v>275</v>
       </c>
       <c r="B276" t="n">
-        <v>154.6093622266761</v>
+        <v>157.1405780686924</v>
       </c>
       <c r="C276" t="n">
-        <v>79.90869787931294</v>
+        <v>81.32260397811734</v>
       </c>
     </row>
     <row r="277">
@@ -3463,10 +3463,10 @@
         <v>276</v>
       </c>
       <c r="B277" t="n">
-        <v>148.7214278460834</v>
+        <v>153.3553357714276</v>
       </c>
       <c r="C277" t="n">
-        <v>76.54964264420539</v>
+        <v>79.0871089758876</v>
       </c>
     </row>
     <row r="278">
@@ -3474,10 +3474,10 @@
         <v>277</v>
       </c>
       <c r="B278" t="n">
-        <v>148.7214278460833</v>
+        <v>153.3553357714277</v>
       </c>
       <c r="C278" t="n">
-        <v>76.54964264420538</v>
+        <v>79.08710897588765</v>
       </c>
     </row>
     <row r="279">
@@ -3485,10 +3485,10 @@
         <v>278</v>
       </c>
       <c r="B279" t="n">
-        <v>140.2039566972015</v>
+        <v>143.4424221489753</v>
       </c>
       <c r="C279" t="n">
-        <v>72.23865987540307</v>
+        <v>74.13262964401582</v>
       </c>
     </row>
     <row r="280">
@@ -3496,10 +3496,10 @@
         <v>279</v>
       </c>
       <c r="B280" t="n">
-        <v>132.0514480670549</v>
+        <v>133.9320593579815</v>
       </c>
       <c r="C280" t="n">
-        <v>67.27192148483668</v>
+        <v>68.44354171009959</v>
       </c>
     </row>
     <row r="281">
@@ -3507,10 +3507,10 @@
         <v>280</v>
       </c>
       <c r="B281" t="n">
-        <v>124.3142860703578</v>
+        <v>124.8785853583079</v>
       </c>
       <c r="C281" t="n">
-        <v>61.68012289745818</v>
+        <v>62.05235007837825</v>
       </c>
     </row>
     <row r="282">
@@ -3518,10 +3518,10 @@
         <v>281</v>
       </c>
       <c r="B282" t="n">
-        <v>117.0402878975349</v>
+        <v>116.3337276515876</v>
       </c>
       <c r="C282" t="n">
-        <v>55.49782253378181</v>
+        <v>54.99557115963271</v>
       </c>
     </row>
     <row r="283">
@@ -3529,10 +3529,10 @@
         <v>282</v>
       </c>
       <c r="B283" t="n">
-        <v>117.0402878975348</v>
+        <v>116.3337276515909</v>
       </c>
       <c r="C283" t="n">
-        <v>55.49782253378199</v>
+        <v>54.99557115962898</v>
       </c>
     </row>
     <row r="284">
@@ -3540,10 +3540,10 @@
         <v>283</v>
       </c>
       <c r="B284" t="n">
-        <v>90.89508951044417</v>
+        <v>86.01815849542635</v>
       </c>
       <c r="C284" t="n">
-        <v>31.44385433138719</v>
+        <v>27.96869051184872</v>
       </c>
     </row>
     <row r="285">
@@ -3551,10 +3551,10 @@
         <v>284</v>
       </c>
       <c r="B285" t="n">
-        <v>90.89508951044414</v>
+        <v>86.01815849542628</v>
       </c>
       <c r="C285" t="n">
-        <v>31.44385433138716</v>
+        <v>27.96869051184865</v>
       </c>
     </row>
     <row r="286">
@@ -3562,10 +3562,10 @@
         <v>285</v>
       </c>
       <c r="B286" t="n">
-        <v>84.95450795646764</v>
+        <v>81.70390093010008</v>
       </c>
       <c r="C286" t="n">
-        <v>26.73402510580918</v>
+        <v>24.70645606009186</v>
       </c>
     </row>
     <row r="287">
@@ -3573,10 +3573,10 @@
         <v>286</v>
       </c>
       <c r="B287" t="n">
-        <v>78.38879173759024</v>
+        <v>76.92156180082492</v>
       </c>
       <c r="C287" t="n">
-        <v>22.94398934519621</v>
+        <v>22.17975378027993</v>
       </c>
     </row>
     <row r="288">
@@ -3584,10 +3584,10 @@
         <v>287</v>
       </c>
       <c r="B288" t="n">
-        <v>71.33923442663787</v>
+        <v>71.79539661532564</v>
       </c>
       <c r="C288" t="n">
-        <v>20.15530824956107</v>
+        <v>20.45423285917288</v>
       </c>
     </row>
     <row r="289">
@@ -3595,10 +3595,10 @@
         <v>288</v>
       </c>
       <c r="B289" t="n">
-        <v>63.95754180955996</v>
+        <v>66.45859422545641</v>
       </c>
       <c r="C289" t="n">
-        <v>18.42799396416545</v>
+        <v>19.57472606005791</v>
       </c>
     </row>
     <row r="290">
@@ -3606,10 +3606,10 @@
         <v>289</v>
       </c>
       <c r="B290" t="n">
-        <v>63.95754180955989</v>
+        <v>66.45859422545647</v>
       </c>
       <c r="C290" t="n">
-        <v>18.4279939641654</v>
+        <v>19.57472606005788</v>
       </c>
     </row>
     <row r="291">
@@ -3617,10 +3617,10 @@
         <v>290</v>
       </c>
       <c r="B291" t="n">
-        <v>63.18212482596008</v>
+        <v>65.19983890290855</v>
       </c>
       <c r="C291" t="n">
-        <v>18.10898582685568</v>
+        <v>19.25923138367525</v>
       </c>
     </row>
     <row r="292">
@@ -3628,10 +3628,10 @@
         <v>291</v>
       </c>
       <c r="B292" t="n">
-        <v>62.63379821915664</v>
+        <v>64.10832373201332</v>
       </c>
       <c r="C292" t="n">
-        <v>17.47465498069079</v>
+        <v>18.55737920224812</v>
       </c>
     </row>
     <row r="293">
@@ -3639,10 +3639,10 @@
         <v>292</v>
       </c>
       <c r="B293" t="n">
-        <v>62.43033158935513</v>
+        <v>63.29893081090962</v>
       </c>
       <c r="C293" t="n">
-        <v>16.66124301822525</v>
+        <v>17.54303953914917</v>
       </c>
     </row>
     <row r="294">
@@ -3650,10 +3650,10 @@
         <v>293</v>
       </c>
       <c r="B294" t="n">
-        <v>62.61542550360738</v>
+        <v>62.85684883827478</v>
       </c>
       <c r="C294" t="n">
-        <v>15.8434545779599</v>
+        <v>16.32297176138445</v>
       </c>
     </row>
     <row r="295">
@@ -3661,10 +3661,10 @@
         <v>294</v>
       </c>
       <c r="B295" t="n">
-        <v>62.61542550360739</v>
+        <v>62.85684883827475</v>
       </c>
       <c r="C295" t="n">
-        <v>15.84345457795995</v>
+        <v>16.32297176138444</v>
       </c>
     </row>
     <row r="296">
@@ -3672,10 +3672,10 @@
         <v>295</v>
       </c>
       <c r="B296" t="n">
-        <v>62.74335889903846</v>
+        <v>61.93115401590743</v>
       </c>
       <c r="C296" t="n">
-        <v>13.93016033157223</v>
+        <v>14.13765087667563</v>
       </c>
     </row>
     <row r="297">
@@ -3683,10 +3683,10 @@
         <v>296</v>
       </c>
       <c r="B297" t="n">
-        <v>61.4896979602627</v>
+        <v>60.17558208706642</v>
       </c>
       <c r="C297" t="n">
-        <v>12.47916202781211</v>
+        <v>12.54062067158631</v>
       </c>
     </row>
     <row r="298">
@@ -3694,10 +3694,10 @@
         <v>297</v>
       </c>
       <c r="B298" t="n">
-        <v>59.57809681555962</v>
+        <v>57.91265800061541</v>
       </c>
       <c r="C298" t="n">
-        <v>12.32802338120991</v>
+        <v>11.82527959750903</v>
       </c>
     </row>
     <row r="299">
@@ -3705,10 +3705,10 @@
         <v>298</v>
       </c>
       <c r="B299" t="n">
-        <v>58.11199421555275</v>
+        <v>55.55811492206863</v>
       </c>
       <c r="C299" t="n">
-        <v>13.56398656560497</v>
+        <v>12.12304656103863</v>
       </c>
     </row>
     <row r="300">
@@ -3716,10 +3716,10 @@
         <v>299</v>
       </c>
       <c r="B300" t="n">
-        <v>58.11199421555271</v>
+        <v>55.55811492206866</v>
       </c>
       <c r="C300" t="n">
-        <v>13.56398656560491</v>
+        <v>12.12304656103869</v>
       </c>
     </row>
     <row r="301">
@@ -3727,10 +3727,10 @@
         <v>300</v>
       </c>
       <c r="B301" t="n">
-        <v>56.46377653967028</v>
+        <v>53.52133062241587</v>
       </c>
       <c r="C301" t="n">
-        <v>14.85099697370581</v>
+        <v>12.30334031706361</v>
       </c>
     </row>
     <row r="302">
@@ -3738,10 +3738,10 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>54.41076036845237</v>
+        <v>51.65320998756054</v>
       </c>
       <c r="C302" t="n">
-        <v>14.45332638343149</v>
+        <v>11.47200319206473</v>
       </c>
     </row>
     <row r="303">
@@ -3749,10 +3749,10 @@
         <v>302</v>
       </c>
       <c r="B303" t="n">
-        <v>53.36231102862509</v>
+        <v>50.42373010052206</v>
       </c>
       <c r="C303" t="n">
-        <v>12.64396979075357</v>
+        <v>9.838180885587814</v>
       </c>
     </row>
     <row r="304">
@@ -3760,10 +3760,10 @@
         <v>303</v>
       </c>
       <c r="B304" t="n">
-        <v>54.03817353101551</v>
+        <v>50.14220041389159</v>
       </c>
       <c r="C304" t="n">
-        <v>10.66502381485784</v>
+        <v>7.812906297459223</v>
       </c>
     </row>
     <row r="305">
@@ -3771,10 +3771,10 @@
         <v>304</v>
       </c>
       <c r="B305" t="n">
-        <v>54.03817353101533</v>
+        <v>50.14220041389162</v>
       </c>
       <c r="C305" t="n">
-        <v>10.6650238148578</v>
+        <v>7.812906297459221</v>
       </c>
     </row>
     <row r="306">
@@ -3782,10 +3782,10 @@
         <v>305</v>
       </c>
       <c r="B306" t="n">
-        <v>54.71403603340566</v>
+        <v>49.57861343112053</v>
       </c>
       <c r="C306" t="n">
-        <v>8.686077838961484</v>
+        <v>4.941498620650112</v>
       </c>
     </row>
     <row r="307">
@@ -3793,10 +3793,10 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>53.66558669357803</v>
+        <v>47.45482212429345</v>
       </c>
       <c r="C307" t="n">
-        <v>6.876721246283156</v>
+        <v>2.928510091464471</v>
       </c>
     </row>
     <row r="308">
@@ -3804,10 +3804,10 @@
         <v>307</v>
       </c>
       <c r="B308" t="n">
-        <v>51.61257052235964</v>
+        <v>44.55736205962607</v>
       </c>
       <c r="C308" t="n">
-        <v>6.479050656008635</v>
+        <v>2.519441017535695</v>
       </c>
     </row>
     <row r="309">
@@ -3815,10 +3815,10 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>49.96435284647661</v>
+        <v>41.95929318666459</v>
       </c>
       <c r="C309" t="n">
-        <v>7.766061064109635</v>
+        <v>3.86578809943395</v>
       </c>
     </row>
     <row r="310">
@@ -3826,10 +3826,10 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>49.9643528464767</v>
+        <v>41.95929318666459</v>
       </c>
       <c r="C310" t="n">
-        <v>7.766061064109592</v>
+        <v>3.865788099433902</v>
       </c>
     </row>
     <row r="311">
@@ -3837,10 +3837,10 @@
         <v>310</v>
       </c>
       <c r="B311" t="n">
-        <v>48.31613517059375</v>
+        <v>39.9515021556531</v>
       </c>
       <c r="C311" t="n">
-        <v>9.053071472210549</v>
+        <v>5.108285829350501</v>
       </c>
     </row>
     <row r="312">
@@ -3848,10 +3848,10 @@
         <v>311</v>
       </c>
       <c r="B312" t="n">
-        <v>46.26311899937543</v>
+        <v>37.59946535042935</v>
       </c>
       <c r="C312" t="n">
-        <v>8.655400881936057</v>
+        <v>5.31552554545481</v>
       </c>
     </row>
     <row r="313">
@@ -3859,10 +3859,10 @@
         <v>312</v>
       </c>
       <c r="B313" t="n">
-        <v>45.21466965954782</v>
+        <v>35.4053411009429</v>
       </c>
       <c r="C313" t="n">
-        <v>6.846044289257807</v>
+        <v>4.443261702988759</v>
       </c>
     </row>
     <row r="314">
@@ -3870,10 +3870,10 @@
         <v>313</v>
       </c>
       <c r="B314" t="n">
-        <v>45.8905321619381</v>
+        <v>33.83757350907891</v>
       </c>
       <c r="C314" t="n">
-        <v>4.867098313361561</v>
+        <v>2.677722065665618</v>
       </c>
     </row>
     <row r="315">
@@ -3881,10 +3881,10 @@
         <v>314</v>
       </c>
       <c r="B315" t="n">
-        <v>45.89053216193822</v>
+        <v>33.83757350907893</v>
       </c>
       <c r="C315" t="n">
-        <v>4.867098313361663</v>
+        <v>2.6777220656656</v>
       </c>
     </row>
     <row r="316">
@@ -3892,10 +3892,10 @@
         <v>315</v>
       </c>
       <c r="B316" t="n">
-        <v>46.51993040963256</v>
+        <v>32.72568128855784</v>
       </c>
       <c r="C316" t="n">
-        <v>2.594556265905129</v>
+        <v>1.246489778977629</v>
       </c>
     </row>
     <row r="317">
@@ -3903,10 +3903,10 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>44.9973078813385</v>
+        <v>31.20508810847269</v>
       </c>
       <c r="C317" t="n">
-        <v>0.7939424405694289</v>
+        <v>0.2603221719290474</v>
       </c>
     </row>
     <row r="318">
@@ -3914,10 +3914,10 @@
         <v>317</v>
       </c>
       <c r="B318" t="n">
-        <v>42.65178124606484</v>
+        <v>29.44481775429363</v>
       </c>
       <c r="C318" t="n">
-        <v>1.037035663182602</v>
+        <v>-0.171161835551783</v>
       </c>
     </row>
     <row r="319">
@@ -3925,10 +3925,10 @@
         <v>318</v>
       </c>
       <c r="B319" t="n">
-        <v>41.53079068718987</v>
+        <v>27.64053568250887</v>
       </c>
       <c r="C319" t="n">
-        <v>3.111636752204735</v>
+        <v>-2.664535259100376e-15</v>
       </c>
     </row>
     <row r="320">
@@ -3936,10 +3936,10 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>41.53079068718988</v>
+        <v>27.64053568250892</v>
       </c>
       <c r="C320" t="n">
-        <v>3.111636752204732</v>
+        <v>7.460698725481052e-14</v>
       </c>
     </row>
     <row r="321">
@@ -3947,10 +3947,10 @@
         <v>320</v>
       </c>
       <c r="B321" t="n">
-        <v>40.66056945751137</v>
+        <v>24.68047201940352</v>
       </c>
       <c r="C321" t="n">
-        <v>4.848112865946254</v>
+        <v>0.6282736636943653</v>
       </c>
     </row>
     <row r="322">
@@ -3958,10 +3958,10 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>38.91807217709012</v>
+        <v>21.67060148535614</v>
       </c>
       <c r="C322" t="n">
-        <v>5.706213972985825</v>
+        <v>0.9403378468398529</v>
       </c>
     </row>
     <row r="323">
@@ -3969,10 +3969,10 @@
         <v>322</v>
       </c>
       <c r="B323" t="n">
-        <v>37.01108466704923</v>
+        <v>18.64460638375544</v>
       </c>
       <c r="C323" t="n">
-        <v>5.33738756568002</v>
+        <v>0.9327003591996004</v>
       </c>
     </row>
     <row r="324">
@@ -3980,10 +3980,10 @@
         <v>323</v>
       </c>
       <c r="B324" t="n">
-        <v>35.71420711519479</v>
+        <v>15.63634946182317</v>
       </c>
       <c r="C324" t="n">
-        <v>3.891447422494954</v>
+        <v>0.6054466689599955</v>
       </c>
     </row>
     <row r="325">
@@ -3991,10 +3991,10 @@
         <v>324</v>
       </c>
       <c r="B325" t="n">
-        <v>35.7142071151948</v>
+        <v>15.63634946182315</v>
       </c>
       <c r="C325" t="n">
-        <v>3.891447422495001</v>
+        <v>0.6054466689600044</v>
       </c>
     </row>
     <row r="326">
@@ -4002,10 +4002,10 @@
         <v>325</v>
       </c>
       <c r="B326" t="n">
-        <v>34.37070458670972</v>
+        <v>11.52559567093245</v>
       </c>
       <c r="C326" t="n">
-        <v>1.865343194946406</v>
+        <v>1.54216977589792</v>
       </c>
     </row>
     <row r="327">
@@ -4013,10 +4013,10 @@
         <v>326</v>
       </c>
       <c r="B327" t="n">
-        <v>32.40316427719875</v>
+        <v>9.228806636600764</v>
       </c>
       <c r="C327" t="n">
-        <v>0.4374487606882163</v>
+        <v>5.077775387411643</v>
       </c>
     </row>
     <row r="328">
@@ -4024,10 +4024,10 @@
         <v>327</v>
       </c>
       <c r="B328" t="n">
-        <v>30.06036377964958</v>
+        <v>10.04384406950787</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.2116916044250408</v>
+        <v>9.214375548335322</v>
       </c>
     </row>
     <row r="329">
@@ -4035,10 +4035,10 @@
         <v>328</v>
       </c>
       <c r="B329" t="n">
-        <v>27.63852892781677</v>
+        <v>13.51014939804397</v>
       </c>
       <c r="C329" t="n">
-        <v>3.375077994860476e-14</v>
+        <v>11.61447435416727</v>
       </c>
     </row>
     <row r="330">
@@ -4046,10 +4046,10 @@
         <v>329</v>
       </c>
       <c r="B330" t="n">
-        <v>27.63852892781677</v>
+        <v>13.51014939804403</v>
       </c>
       <c r="C330" t="n">
-        <v>-1.77635683940025e-14</v>
+        <v>11.61447435416717</v>
       </c>
     </row>
     <row r="331">
@@ -4057,10 +4057,10 @@
         <v>330</v>
       </c>
       <c r="B331" t="n">
-        <v>24.50232843312333</v>
+        <v>19.39013346241222</v>
       </c>
       <c r="C331" t="n">
-        <v>0.6609894756553594</v>
+        <v>13.75109546966134</v>
       </c>
     </row>
     <row r="332">
@@ -4068,10 +4068,10 @@
         <v>331</v>
       </c>
       <c r="B332" t="n">
-        <v>21.31057883944615</v>
+        <v>24.53571430137291</v>
       </c>
       <c r="C332" t="n">
-        <v>0.9532139802816388</v>
+        <v>17.30951649844918</v>
       </c>
     </row>
     <row r="333">
@@ -4079,10 +4079,10 @@
         <v>332</v>
       </c>
       <c r="B333" t="n">
-        <v>18.10649068247103</v>
+        <v>28.61021989862881</v>
       </c>
       <c r="C333" t="n">
-        <v>0.8727173208834564</v>
+        <v>22.05691226100464</v>
       </c>
     </row>
     <row r="334">
@@ -4090,10 +4090,10 @@
         <v>333</v>
       </c>
       <c r="B334" t="n">
-        <v>14.93344153978791</v>
+        <v>31.3470579961288</v>
       </c>
       <c r="C334" t="n">
-        <v>0.4205892771165907</v>
+        <v>27.68266373227246</v>
       </c>
     </row>
     <row r="335">
@@ -4101,10 +4101,10 @@
         <v>334</v>
       </c>
       <c r="B335" t="n">
-        <v>14.93344153978789</v>
+        <v>31.34705799612803</v>
       </c>
       <c r="C335" t="n">
-        <v>0.4205892771166191</v>
+        <v>27.68266373227271</v>
       </c>
     </row>
     <row r="336">
@@ -4112,10 +4112,10 @@
         <v>335</v>
       </c>
       <c r="B336" t="n">
-        <v>11.53766714009393</v>
+        <v>31.92975825527402</v>
       </c>
       <c r="C336" t="n">
-        <v>1.060432287964813</v>
+        <v>28.95697153659784</v>
       </c>
     </row>
     <row r="337">
@@ -4123,10 +4123,10 @@
         <v>336</v>
       </c>
       <c r="B337" t="n">
-        <v>9.550797657522725</v>
+        <v>32.76384113754223</v>
       </c>
       <c r="C337" t="n">
-        <v>3.887627454799863</v>
+        <v>30.08289592023996</v>
       </c>
     </row>
     <row r="338">
@@ -4134,10 +4134,10 @@
         <v>337</v>
       </c>
       <c r="B338" t="n">
-        <v>10.09924754195942</v>
+        <v>33.8131077415355</v>
       </c>
       <c r="C338" t="n">
-        <v>7.299355107530892</v>
+        <v>31.01157216410387</v>
       </c>
     </row>
     <row r="339">
@@ -4145,10 +4145,10 @@
         <v>338</v>
       </c>
       <c r="B339" t="n">
-        <v>12.87208450505468</v>
+        <v>35.03202026861919</v>
       </c>
       <c r="C339" t="n">
-        <v>9.361407005093335</v>
+        <v>31.70269604843371</v>
       </c>
     </row>
     <row r="340">
@@ -4156,10 +4156,10 @@
         <v>339</v>
       </c>
       <c r="B340" t="n">
-        <v>12.87208450505467</v>
+        <v>35.03202026861915</v>
       </c>
       <c r="C340" t="n">
-        <v>9.361407005093323</v>
+        <v>31.70269604843373</v>
       </c>
     </row>
     <row r="341">
@@ -4167,10 +4167,10 @@
         <v>340</v>
       </c>
       <c r="B341" t="n">
-        <v>18.70986568322471</v>
+        <v>36.58527661209234</v>
       </c>
       <c r="C341" t="n">
-        <v>11.7066945145653</v>
+        <v>33.06300201102949</v>
       </c>
     </row>
     <row r="342">
@@ -4178,10 +4178,10 @@
         <v>341</v>
       </c>
       <c r="B342" t="n">
-        <v>23.75931905457217</v>
+        <v>37.06780857499785</v>
       </c>
       <c r="C342" t="n">
-        <v>15.45943794262824</v>
+        <v>35.07053793478971</v>
       </c>
     </row>
     <row r="343">
@@ -4189,10 +4189,10 @@
         <v>342</v>
       </c>
       <c r="B343" t="n">
-        <v>27.6884425778558</v>
+        <v>36.30243382504917</v>
       </c>
       <c r="C343" t="n">
-        <v>20.37289405060974</v>
+        <v>36.98815079262997</v>
       </c>
     </row>
     <row r="344">
@@ -4200,10 +4200,10 @@
         <v>343</v>
       </c>
       <c r="B344" t="n">
-        <v>30.23889600630334</v>
+        <v>34.57019257034474</v>
       </c>
       <c r="C344" t="n">
-        <v>26.12400263031871</v>
+        <v>38.11170667282164</v>
       </c>
     </row>
     <row r="345">
@@ -4211,10 +4211,10 @@
         <v>344</v>
       </c>
       <c r="B345" t="n">
-        <v>30.23889600630332</v>
+        <v>34.57019257034475</v>
       </c>
       <c r="C345" t="n">
-        <v>26.12400263031869</v>
+        <v>38.11170667282159</v>
       </c>
     </row>
     <row r="346">
@@ -4222,10 +4222,10 @@
         <v>345</v>
       </c>
       <c r="B346" t="n">
-        <v>30.90998309387831</v>
+        <v>30.75791913909092</v>
       </c>
       <c r="C346" t="n">
-        <v>27.65402641657521</v>
+        <v>40.84790752381862</v>
       </c>
     </row>
     <row r="347">
@@ -4233,10 +4233,10 @@
         <v>346</v>
       </c>
       <c r="B347" t="n">
-        <v>31.93741065529247</v>
+        <v>29.64992593558576</v>
       </c>
       <c r="C347" t="n">
-        <v>28.97149492537047</v>
+        <v>45.40779511811601</v>
       </c>
     </row>
     <row r="348">
@@ -4244,10 +4244,10 @@
         <v>347</v>
       </c>
       <c r="B348" t="n">
-        <v>33.25781100601138</v>
+        <v>31.78153453007926</v>
       </c>
       <c r="C348" t="n">
-        <v>29.99515188912445</v>
+        <v>49.58828176580695</v>
       </c>
     </row>
     <row r="349">
@@ -4255,10 +4255,10 @@
         <v>348</v>
       </c>
       <c r="B349" t="n">
-        <v>34.78974705399489</v>
+        <v>36.12286851506936</v>
       </c>
       <c r="C349" t="n">
-        <v>30.66186217891251</v>
+        <v>51.36958551374294</v>
       </c>
     </row>
     <row r="350">
@@ -4266,10 +4266,10 @@
         <v>349</v>
       </c>
       <c r="B350" t="n">
-        <v>34.78974705399489</v>
+        <v>36.12286851506937</v>
       </c>
       <c r="C350" t="n">
-        <v>30.66186217891248</v>
+        <v>51.369585513743</v>
       </c>
     </row>
     <row r="351">
@@ -4277,10 +4277,10 @@
         <v>350</v>
       </c>
       <c r="B351" t="n">
-        <v>36.50902492374558</v>
+        <v>40.56279868046652</v>
       </c>
       <c r="C351" t="n">
-        <v>31.82726026492185</v>
+        <v>53.35328904422808</v>
       </c>
     </row>
     <row r="352">
@@ -4288,10 +4288,10 @@
         <v>351</v>
       </c>
       <c r="B352" t="n">
-        <v>37.23230351528464</v>
+        <v>42.36244659038305</v>
       </c>
       <c r="C352" t="n">
-        <v>33.77429317972068</v>
+        <v>57.87095735551385</v>
       </c>
     </row>
     <row r="353">
@@ -4299,10 +4299,10 @@
         <v>352</v>
       </c>
       <c r="B353" t="n">
-        <v>36.69083606079249</v>
+        <v>40.50265856195619</v>
       </c>
       <c r="C353" t="n">
-        <v>35.77950690598892</v>
+        <v>62.36420206950203</v>
       </c>
     </row>
     <row r="354">
@@ -4310,10 +4310,10 @@
         <v>353</v>
       </c>
       <c r="B354" t="n">
-        <v>35.08581423105344</v>
+        <v>36.03664606397999</v>
       </c>
       <c r="C354" t="n">
-        <v>37.09782933178234</v>
+        <v>64.28846606864114</v>
       </c>
     </row>
     <row r="355">
@@ -4321,10 +4321,10 @@
         <v>354</v>
       </c>
       <c r="B355" t="n">
-        <v>35.08581423105342</v>
+        <v>36.03664606397996</v>
       </c>
       <c r="C355" t="n">
-        <v>37.09782933178236</v>
+        <v>64.28846606864106</v>
       </c>
     </row>
     <row r="356">
@@ -4332,10 +4332,10 @@
         <v>355</v>
       </c>
       <c r="B356" t="n">
-        <v>32.05808968382479</v>
+        <v>34.14947112266045</v>
       </c>
       <c r="C356" t="n">
-        <v>39.58829753693551</v>
+        <v>64.81438618888259</v>
       </c>
     </row>
     <row r="357">
@@ -4343,10 +4343,10 @@
         <v>356</v>
       </c>
       <c r="B357" t="n">
-        <v>31.04407418890523</v>
+        <v>32.74742335259161</v>
       </c>
       <c r="C357" t="n">
-        <v>43.37529111903101</v>
+        <v>66.18270021806747</v>
       </c>
     </row>
     <row r="358">
@@ -4354,10 +4354,10 @@
         <v>357</v>
       </c>
       <c r="B358" t="n">
-        <v>32.42220406597072</v>
+        <v>32.17570702216157</v>
       </c>
       <c r="C358" t="n">
-        <v>47.04548264764488</v>
+        <v>68.05650961860391</v>
       </c>
     </row>
     <row r="359">
@@ -4365,10 +4365,10 @@
         <v>358</v>
       </c>
       <c r="B359" t="n">
-        <v>35.6781534478869</v>
+        <v>32.57508689116305</v>
       </c>
       <c r="C359" t="n">
-        <v>49.22913587954073</v>
+        <v>69.97445564293712</v>
       </c>
     </row>
     <row r="360">
@@ -4376,10 +4376,10 @@
         <v>359</v>
       </c>
       <c r="B360" t="n">
-        <v>35.67815344788687</v>
+        <v>32.57508689116306</v>
       </c>
       <c r="C360" t="n">
-        <v>49.22913587954072</v>
+        <v>69.97445564293713</v>
       </c>
     </row>
     <row r="361">
@@ -4387,10 +4387,10 @@
         <v>360</v>
       </c>
       <c r="B361" t="n">
-        <v>39.4646842087747</v>
+        <v>32.98378077955976</v>
       </c>
       <c r="C361" t="n">
-        <v>51.74730412054086</v>
+        <v>71.75652514882681</v>
       </c>
     </row>
     <row r="362">
@@ -4398,10 +4398,10 @@
         <v>361</v>
       </c>
       <c r="B362" t="n">
-        <v>41.11286405482365</v>
+        <v>32.5567851076763</v>
       </c>
       <c r="C362" t="n">
-        <v>55.98552186957282</v>
+        <v>73.53429822614221</v>
       </c>
     </row>
     <row r="363">
@@ -4409,10 +4409,10 @@
         <v>362</v>
       </c>
       <c r="B363" t="n">
-        <v>40.02243958991732</v>
+        <v>31.38331001079693</v>
       </c>
       <c r="C363" t="n">
-        <v>60.40026546116058</v>
+        <v>74.93635336601319</v>
       </c>
     </row>
     <row r="364">
@@ -4420,10 +4420,10 @@
         <v>363</v>
       </c>
       <c r="B364" t="n">
-        <v>36.59053433782497</v>
+        <v>29.70852395089578</v>
       </c>
       <c r="C364" t="n">
-        <v>63.38372198569591</v>
+        <v>75.66976598643606</v>
       </c>
     </row>
     <row r="365">
@@ -4431,10 +4431,10 @@
         <v>364</v>
       </c>
       <c r="B365" t="n">
-        <v>36.59053433782495</v>
+        <v>29.70852395089577</v>
       </c>
       <c r="C365" t="n">
-        <v>63.38372198569595</v>
+        <v>75.66976598643603</v>
       </c>
     </row>
     <row r="366">
@@ -4442,10 +4442,10 @@
         <v>365</v>
       </c>
       <c r="B366" t="n">
-        <v>35.40677021087608</v>
+        <v>27.54319015206047</v>
       </c>
       <c r="C366" t="n">
-        <v>64.25833066129779</v>
+        <v>76.54279068744495</v>
       </c>
     </row>
     <row r="367">
@@ -4453,10 +4453,10 @@
         <v>366</v>
       </c>
       <c r="B367" t="n">
-        <v>34.72708773211705</v>
+        <v>25.89228084498964</v>
       </c>
       <c r="C367" t="n">
-        <v>65.56380742162597</v>
+        <v>78.19365138683091</v>
       </c>
     </row>
     <row r="368">
@@ -4464,10 +4464,10 @@
         <v>367</v>
       </c>
       <c r="B368" t="n">
-        <v>34.68946223520858</v>
+        <v>25.0191923895472</v>
       </c>
       <c r="C368" t="n">
-        <v>67.03514088677635</v>
+        <v>80.35895947990295</v>
       </c>
     </row>
     <row r="369">
@@ -4475,10 +4475,10 @@
         <v>368</v>
       </c>
       <c r="B369" t="n">
-        <v>35.30153168442419</v>
+        <v>25.063222759291</v>
       </c>
       <c r="C369" t="n">
-        <v>68.37365081689487</v>
+        <v>82.69324821857485</v>
       </c>
     </row>
     <row r="370">
@@ -4486,10 +4486,10 @@
         <v>369</v>
       </c>
       <c r="B370" t="n">
-        <v>35.3015316844242</v>
+        <v>25.063222759291</v>
       </c>
       <c r="C370" t="n">
-        <v>68.37365081689492</v>
+        <v>82.69324821857487</v>
       </c>
     </row>
     <row r="371">
@@ -4497,10 +4497,10 @@
         <v>370</v>
       </c>
       <c r="B371" t="n">
-        <v>36.24121033657219</v>
+        <v>25.1318519686903</v>
       </c>
       <c r="C371" t="n">
-        <v>71.3955266799363</v>
+        <v>84.8865598308315</v>
       </c>
     </row>
     <row r="372">
@@ -4508,10 +4508,10 @@
         <v>371</v>
       </c>
       <c r="B372" t="n">
-        <v>34.98617808198472</v>
+        <v>24.38761866051052</v>
       </c>
       <c r="C372" t="n">
-        <v>74.3006297316162</v>
+        <v>86.95088601141401</v>
       </c>
     </row>
     <row r="373">
@@ -4519,10 +4519,10 @@
         <v>372</v>
       </c>
       <c r="B373" t="n">
-        <v>32.14177303358358</v>
+        <v>22.93521580869873</v>
       </c>
       <c r="C373" t="n">
-        <v>75.68774530775427</v>
+        <v>88.59583335187558</v>
       </c>
     </row>
     <row r="374">
@@ -4530,10 +4530,10 @@
         <v>373</v>
       </c>
       <c r="B374" t="n">
-        <v>29.07993346474037</v>
+        <v>20.97895619024857</v>
       </c>
       <c r="C374" t="n">
-        <v>74.88782771474814</v>
+        <v>89.59000340878931</v>
       </c>
     </row>
     <row r="375">
@@ -4541,10 +4541,10 @@
         <v>374</v>
       </c>
       <c r="B375" t="n">
-        <v>29.07993346474069</v>
+        <v>20.97895619024856</v>
       </c>
       <c r="C375" t="n">
-        <v>74.88782771474744</v>
+        <v>89.59000340878924</v>
       </c>
     </row>
     <row r="376">
@@ -4552,10 +4552,10 @@
         <v>375</v>
       </c>
       <c r="B376" t="n">
-        <v>25.91866505878456</v>
+        <v>19.22991354432567</v>
       </c>
       <c r="C376" t="n">
-        <v>74.65907698275055</v>
+        <v>90.43012727960186</v>
       </c>
     </row>
     <row r="377">
@@ -4563,10 +4563,10 @@
         <v>376</v>
       </c>
       <c r="B377" t="n">
-        <v>23.55144906755481</v>
+        <v>17.85090016285368</v>
       </c>
       <c r="C377" t="n">
-        <v>76.76673760124483</v>
+        <v>91.79514756856732</v>
       </c>
     </row>
     <row r="378">
@@ -4574,10 +4574,10 @@
         <v>377</v>
       </c>
       <c r="B378" t="n">
-        <v>23.41317058372933</v>
+        <v>16.99298209948282</v>
       </c>
       <c r="C378" t="n">
-        <v>79.93325365091148</v>
+        <v>93.53553111598096</v>
       </c>
     </row>
     <row r="379">
@@ -4585,10 +4585,10 @@
         <v>378</v>
       </c>
       <c r="B379" t="n">
-        <v>25.58764694202299</v>
+        <v>16.7501412531054</v>
       </c>
       <c r="C379" t="n">
-        <v>82.23924528123182</v>
+        <v>95.46062504067575</v>
       </c>
     </row>
     <row r="380">
@@ -4596,10 +4596,10 @@
         <v>379</v>
       </c>
       <c r="B380" t="n">
-        <v>25.58764694202361</v>
+        <v>16.75014125310533</v>
       </c>
       <c r="C380" t="n">
-        <v>82.23924528123297</v>
+        <v>95.46062504067575</v>
       </c>
     </row>
     <row r="381">
@@ -4607,10 +4607,10 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>27.55739675059016</v>
+        <v>16.0082929493689</v>
       </c>
       <c r="C381" t="n">
-        <v>84.32782626411515</v>
+        <v>98.99282321999996</v>
       </c>
     </row>
     <row r="382">
@@ -4618,10 +4618,10 @@
         <v>381</v>
       </c>
       <c r="B382" t="n">
-        <v>27.43276763796945</v>
+        <v>13.67600005670479</v>
       </c>
       <c r="C382" t="n">
-        <v>87.19602298238475</v>
+        <v>101.7473055210152</v>
       </c>
     </row>
     <row r="383">
@@ -4629,10 +4629,10 @@
         <v>382</v>
       </c>
       <c r="B383" t="n">
-        <v>25.28927759363773</v>
+        <v>10.31443316180263</v>
       </c>
       <c r="C383" t="n">
-        <v>89.1058751390335</v>
+        <v>103.0613187990592</v>
       </c>
     </row>
     <row r="384">
@@ -4640,10 +4640,10 @@
         <v>383</v>
       </c>
       <c r="B384" t="n">
-        <v>22.42575684438939</v>
+        <v>6.732415407133965</v>
       </c>
       <c r="C384" t="n">
-        <v>88.90012347068227</v>
+        <v>102.6186996749622</v>
       </c>
     </row>
     <row r="385">
@@ -4651,10 +4651,10 @@
         <v>384</v>
       </c>
       <c r="B385" t="n">
-        <v>22.42575684438881</v>
+        <v>6.732415407133942</v>
       </c>
       <c r="C385" t="n">
-        <v>88.90012347068351</v>
+        <v>102.6186996749623</v>
       </c>
     </row>
     <row r="386">
@@ -4662,10 +4662,10 @@
         <v>385</v>
       </c>
       <c r="B386" t="n">
-        <v>18.7942942772216</v>
+        <v>4.780282380955402</v>
       </c>
       <c r="C386" t="n">
-        <v>88.37183780185276</v>
+        <v>102.2582227761548</v>
       </c>
     </row>
     <row r="387">
@@ -4673,10 +4673,10 @@
         <v>386</v>
       </c>
       <c r="B387" t="n">
-        <v>15.59092417626686</v>
+        <v>2.83225487739155</v>
       </c>
       <c r="C387" t="n">
-        <v>90.16209647616152</v>
+        <v>102.6402643862311</v>
       </c>
     </row>
     <row r="388">
@@ -4684,10 +4684,10 @@
         <v>387</v>
       </c>
       <c r="B388" t="n">
-        <v>14.13797298553839</v>
+        <v>1.160880380383273</v>
       </c>
       <c r="C388" t="n">
-        <v>93.53189453568812</v>
+        <v>103.711373268288</v>
       </c>
     </row>
     <row r="389">
@@ -4695,120 +4695,10 @@
         <v>388</v>
       </c>
       <c r="B389" t="n">
-        <v>15.03520773813329</v>
+        <v>1.751487843648647e-12</v>
       </c>
       <c r="C389" t="n">
-        <v>97.09020536013341</v>
-      </c>
-    </row>
-    <row r="390">
-      <c r="A390" t="n">
-        <v>389</v>
-      </c>
-      <c r="B390" t="n">
-        <v>15.03520773813805</v>
-      </c>
-      <c r="C390" t="n">
-        <v>97.09020536013031</v>
-      </c>
-    </row>
-    <row r="391">
-      <c r="A391" t="n">
-        <v>390</v>
-      </c>
-      <c r="B391" t="n">
-        <v>15.75726874975513</v>
-      </c>
-      <c r="C391" t="n">
-        <v>100.2835391119707</v>
-      </c>
-    </row>
-    <row r="392">
-      <c r="A392" t="n">
-        <v>391</v>
-      </c>
-      <c r="B392" t="n">
-        <v>14.24262200581481</v>
-      </c>
-      <c r="C392" t="n">
-        <v>103.1860548821624</v>
-      </c>
-    </row>
-    <row r="393">
-      <c r="A393" t="n">
-        <v>392</v>
-      </c>
-      <c r="B393" t="n">
-        <v>11.21016360603469</v>
-      </c>
-      <c r="C393" t="n">
-        <v>104.4201329221353</v>
-      </c>
-    </row>
-    <row r="394">
-      <c r="A394" t="n">
-        <v>393</v>
-      </c>
-      <c r="B394" t="n">
-        <v>8.099187910554772</v>
-      </c>
-      <c r="C394" t="n">
-        <v>103.4000433293673</v>
-      </c>
-    </row>
-    <row r="395">
-      <c r="A395" t="n">
-        <v>394</v>
-      </c>
-      <c r="B395" t="n">
-        <v>8.099187910555639</v>
-      </c>
-      <c r="C395" t="n">
-        <v>103.4000433293661</v>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" t="n">
-        <v>395</v>
-      </c>
-      <c r="B396" t="n">
-        <v>5.956499448615382</v>
-      </c>
-      <c r="C396" t="n">
-        <v>102.3829987868652</v>
-      </c>
-    </row>
-    <row r="397">
-      <c r="A397" t="n">
-        <v>396</v>
-      </c>
-      <c r="B397" t="n">
-        <v>3.584754581069789</v>
-      </c>
-      <c r="C397" t="n">
-        <v>102.4008797721254</v>
-      </c>
-    </row>
-    <row r="398">
-      <c r="A398" t="n">
-        <v>397</v>
-      </c>
-      <c r="B398" t="n">
-        <v>1.457644151789985</v>
-      </c>
-      <c r="C398" t="n">
-        <v>103.4501150498453</v>
-      </c>
-    </row>
-    <row r="399">
-      <c r="A399" t="n">
-        <v>398</v>
-      </c>
-      <c r="B399" t="n">
-        <v>1.295852314342483e-12</v>
-      </c>
-      <c r="C399" t="n">
-        <v>105.321148714192</v>
+        <v>105.3216911527183</v>
       </c>
     </row>
   </sheetData>
